--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="542">
   <si>
     <t>trade_time</t>
   </si>
@@ -316,12 +316,12 @@
     <t>2021-03-22</t>
   </si>
   <si>
+    <t>2021-09-09</t>
+  </si>
+  <si>
     <t>2021-08-30</t>
   </si>
   <si>
-    <t>2021-09-09</t>
-  </si>
-  <si>
     <t>2016-12-12</t>
   </si>
   <si>
@@ -736,12 +736,12 @@
     <t>2021-04-07</t>
   </si>
   <si>
+    <t>2021-09-14</t>
+  </si>
+  <si>
     <t>2021-09-03</t>
   </si>
   <si>
-    <t>2021-09-13</t>
-  </si>
-  <si>
     <t>2016-10-31</t>
   </si>
   <si>
@@ -1633,7 +1633,13 @@
     <t>2020-11-05</t>
   </si>
   <si>
+    <t>2021-08-24</t>
+  </si>
+  <si>
     <t>2021-08-25</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
   </si>
 </sst>
 </file>
@@ -1991,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P983"/>
+  <dimension ref="A1:P985"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51049,40 +51055,40 @@
         <v>100</v>
       </c>
       <c r="C982">
-        <v>1.205527045337084</v>
+        <v>1.670179993880013</v>
       </c>
       <c r="D982" t="s">
         <v>240</v>
       </c>
       <c r="E982">
-        <v>1.459905895755821</v>
+        <v>1.472017059463273</v>
       </c>
       <c r="F982">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G982">
-        <v>0.01299447295466291</v>
+        <v>0.01410982000611999</v>
       </c>
       <c r="H982">
-        <v>0.01366009410424418</v>
+        <v>0.01316798294053673</v>
       </c>
       <c r="I982">
-        <v>0.2543788504187363</v>
+        <v>0.1981629344167404</v>
       </c>
       <c r="J982">
-        <v>1.142339719895914</v>
+        <v>1.12677898661594</v>
       </c>
       <c r="K982">
-        <v>5.16</v>
+        <v>5.52</v>
       </c>
       <c r="L982">
-        <v>7.1</v>
+        <v>7.89</v>
       </c>
       <c r="M982">
-        <v>5.34</v>
+        <v>5.19</v>
       </c>
       <c r="N982">
-        <v>7.56</v>
+        <v>7.32</v>
       </c>
       <c r="O982">
         <v>1</v>
@@ -51093,52 +51099,152 @@
     </row>
     <row r="983" spans="1:16">
       <c r="A983" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B983" t="s">
         <v>101</v>
       </c>
       <c r="C983">
-        <v>1.584284746174556</v>
+        <v>1.205527045337084</v>
       </c>
       <c r="D983" t="s">
         <v>241</v>
       </c>
       <c r="E983">
-        <v>1.442825129368311</v>
+        <v>1.459905895755821</v>
       </c>
       <c r="F983">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G983">
-        <v>0.01419571525382544</v>
+        <v>0.01299447295466291</v>
       </c>
       <c r="H983">
-        <v>0.01391717487063169</v>
+        <v>0.01366009410424418</v>
       </c>
       <c r="I983">
-        <v>0.1414596168062454</v>
+        <v>0.2543788504187363</v>
       </c>
       <c r="J983">
         <v>1.142339719895914</v>
       </c>
       <c r="K983">
+        <v>5.16</v>
+      </c>
+      <c r="L983">
+        <v>7.1</v>
+      </c>
+      <c r="M983">
+        <v>5.34</v>
+      </c>
+      <c r="N983">
+        <v>7.56</v>
+      </c>
+      <c r="O983">
+        <v>1</v>
+      </c>
+      <c r="P983" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="984" spans="1:16">
+      <c r="A984" s="1">
+        <v>1</v>
+      </c>
+      <c r="B984" t="s">
+        <v>100</v>
+      </c>
+      <c r="C984">
+        <v>1.584284746174556</v>
+      </c>
+      <c r="D984" t="s">
+        <v>240</v>
+      </c>
+      <c r="E984">
+        <v>1.391256853740208</v>
+      </c>
+      <c r="F984">
+        <v>-1</v>
+      </c>
+      <c r="G984">
+        <v>0.01419571525382544</v>
+      </c>
+      <c r="H984">
+        <v>0.01324874314625979</v>
+      </c>
+      <c r="I984">
+        <v>0.1930278924343485</v>
+      </c>
+      <c r="J984">
+        <v>1.142339719895914</v>
+      </c>
+      <c r="K984">
         <v>5.52</v>
       </c>
-      <c r="L983">
+      <c r="L984">
         <v>7.89</v>
       </c>
-      <c r="M983">
-        <v>5.46</v>
-      </c>
-      <c r="N983">
-        <v>7.68</v>
-      </c>
-      <c r="O983">
-        <v>1</v>
-      </c>
-      <c r="P983" t="s">
-        <v>539</v>
+      <c r="M984">
+        <v>5.19</v>
+      </c>
+      <c r="N984">
+        <v>7.32</v>
+      </c>
+      <c r="O984">
+        <v>1</v>
+      </c>
+      <c r="P984" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="985" spans="1:16">
+      <c r="A985" s="1">
+        <v>0</v>
+      </c>
+      <c r="B985" t="s">
+        <v>100</v>
+      </c>
+      <c r="C985">
+        <v>1.41577114840967</v>
+      </c>
+      <c r="D985" t="s">
+        <v>240</v>
+      </c>
+      <c r="E985">
+        <v>1.232817438450395</v>
+      </c>
+      <c r="F985">
+        <v>-1</v>
+      </c>
+      <c r="G985">
+        <v>0.01436422885159033</v>
+      </c>
+      <c r="H985">
+        <v>0.01340718256154961</v>
+      </c>
+      <c r="I985">
+        <v>0.1829537099592748</v>
+      </c>
+      <c r="J985">
+        <v>1.172867545577958</v>
+      </c>
+      <c r="K985">
+        <v>5.52</v>
+      </c>
+      <c r="L985">
+        <v>7.89</v>
+      </c>
+      <c r="M985">
+        <v>5.19</v>
+      </c>
+      <c r="N985">
+        <v>7.32</v>
+      </c>
+      <c r="O985">
+        <v>1</v>
+      </c>
+      <c r="P985" t="s">
+        <v>541</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="539">
   <si>
     <t>trade_time</t>
   </si>
@@ -733,7 +733,7 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-09-23</t>
+    <t>2021-09-27</t>
   </si>
   <si>
     <t>2016-10-31</t>
@@ -1631,15 +1631,6 @@
   </si>
   <si>
     <t>2021-08-25</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>2021-09-07</t>
   </si>
 </sst>
 </file>
@@ -1997,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P986"/>
+  <dimension ref="A1:P983"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51061,7 +51052,7 @@
         <v>239</v>
       </c>
       <c r="E982">
-        <v>1.752159378392547</v>
+        <v>1.765962747991026</v>
       </c>
       <c r="F982">
         <v>-1</v>
@@ -51070,10 +51061,10 @@
         <v>0.01306135935334738</v>
       </c>
       <c r="H982">
-        <v>0.01326784062160745</v>
+        <v>0.01321403725200898</v>
       </c>
       <c r="I982">
-        <v>0.08648126826007285</v>
+        <v>0.07267789866159369</v>
       </c>
       <c r="J982">
         <v>1.12677898661594</v>
@@ -51085,10 +51076,10 @@
         <v>7.45</v>
       </c>
       <c r="M982">
-        <v>5.11</v>
+        <v>5.08</v>
       </c>
       <c r="N982">
-        <v>7.51</v>
+        <v>7.49</v>
       </c>
       <c r="O982">
         <v>1</v>
@@ -51111,7 +51102,7 @@
         <v>239</v>
       </c>
       <c r="E983">
-        <v>1.67264403133188</v>
+        <v>1.686914222928758</v>
       </c>
       <c r="F983">
         <v>-1</v>
@@ -51120,10 +51111,10 @@
         <v>0.01313885180508165</v>
       </c>
       <c r="H983">
-        <v>0.01334735596866812</v>
+        <v>0.01329308577707124</v>
       </c>
       <c r="I983">
-        <v>0.08850416358646918</v>
+        <v>0.07423397198959147</v>
       </c>
       <c r="J983">
         <v>1.142339719895914</v>
@@ -51135,166 +51126,16 @@
         <v>7.45</v>
       </c>
       <c r="M983">
-        <v>5.11</v>
+        <v>5.08</v>
       </c>
       <c r="N983">
-        <v>7.51</v>
+        <v>7.49</v>
       </c>
       <c r="O983">
         <v>1</v>
       </c>
       <c r="P983" t="s">
         <v>538</v>
-      </c>
-    </row>
-    <row r="984" spans="1:16">
-      <c r="A984" s="1">
-        <v>0</v>
-      </c>
-      <c r="B984" t="s">
-        <v>100</v>
-      </c>
-      <c r="C984">
-        <v>1.609119623021766</v>
-      </c>
-      <c r="D984" t="s">
-        <v>239</v>
-      </c>
-      <c r="E984">
-        <v>1.516646842096631</v>
-      </c>
-      <c r="F984">
-        <v>-1</v>
-      </c>
-      <c r="G984">
-        <v>0.01329088037697823</v>
-      </c>
-      <c r="H984">
-        <v>0.01350335315790337</v>
-      </c>
-      <c r="I984">
-        <v>0.09247278092513511</v>
-      </c>
-      <c r="J984">
-        <v>1.172867545577958</v>
-      </c>
-      <c r="K984">
-        <v>4.98</v>
-      </c>
-      <c r="L984">
-        <v>7.45</v>
-      </c>
-      <c r="M984">
-        <v>5.11</v>
-      </c>
-      <c r="N984">
-        <v>7.51</v>
-      </c>
-      <c r="O984">
-        <v>1</v>
-      </c>
-      <c r="P984" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="985" spans="1:16">
-      <c r="A985" s="1">
-        <v>0</v>
-      </c>
-      <c r="B985" t="s">
-        <v>100</v>
-      </c>
-      <c r="C985">
-        <v>1.547660564422871</v>
-      </c>
-      <c r="D985" t="s">
-        <v>239</v>
-      </c>
-      <c r="E985">
-        <v>1.453583430562423</v>
-      </c>
-      <c r="F985">
-        <v>-1</v>
-      </c>
-      <c r="G985">
-        <v>0.01335233943557713</v>
-      </c>
-      <c r="H985">
-        <v>0.01356641656943758</v>
-      </c>
-      <c r="I985">
-        <v>0.09407713386044758</v>
-      </c>
-      <c r="J985">
-        <v>1.18520872200344</v>
-      </c>
-      <c r="K985">
-        <v>4.98</v>
-      </c>
-      <c r="L985">
-        <v>7.45</v>
-      </c>
-      <c r="M985">
-        <v>5.11</v>
-      </c>
-      <c r="N985">
-        <v>7.51</v>
-      </c>
-      <c r="O985">
-        <v>1</v>
-      </c>
-      <c r="P985" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="986" spans="1:16">
-      <c r="A986" s="1">
-        <v>0</v>
-      </c>
-      <c r="B986" t="s">
-        <v>100</v>
-      </c>
-      <c r="C986">
-        <v>1.532154426162114</v>
-      </c>
-      <c r="D986" t="s">
-        <v>239</v>
-      </c>
-      <c r="E986">
-        <v>1.437672513592048</v>
-      </c>
-      <c r="F986">
-        <v>-1</v>
-      </c>
-      <c r="G986">
-        <v>0.01336784557383789</v>
-      </c>
-      <c r="H986">
-        <v>0.01358232748640795</v>
-      </c>
-      <c r="I986">
-        <v>0.09448191257006577</v>
-      </c>
-      <c r="J986">
-        <v>1.188322404385118</v>
-      </c>
-      <c r="K986">
-        <v>4.98</v>
-      </c>
-      <c r="L986">
-        <v>7.45</v>
-      </c>
-      <c r="M986">
-        <v>5.11</v>
-      </c>
-      <c r="N986">
-        <v>7.51</v>
-      </c>
-      <c r="O986">
-        <v>1</v>
-      </c>
-      <c r="P986" t="s">
-        <v>541</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="539">
   <si>
     <t>trade_time</t>
   </si>
@@ -1628,6 +1628,9 @@
   </si>
   <si>
     <t>2021-08-25</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
   </si>
 </sst>
 </file>
@@ -1985,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P982"/>
+  <dimension ref="A1:P983"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51085,6 +51088,56 @@
         <v>537</v>
       </c>
     </row>
+    <row r="983" spans="1:16">
+      <c r="A983" s="1">
+        <v>0</v>
+      </c>
+      <c r="B983" t="s">
+        <v>100</v>
+      </c>
+      <c r="C983">
+        <v>1.547660564422871</v>
+      </c>
+      <c r="D983" t="s">
+        <v>239</v>
+      </c>
+      <c r="E983">
+        <v>1.183583430562424</v>
+      </c>
+      <c r="F983">
+        <v>-1</v>
+      </c>
+      <c r="G983">
+        <v>0.01335233943557713</v>
+      </c>
+      <c r="H983">
+        <v>0.01329641656943758</v>
+      </c>
+      <c r="I983">
+        <v>0.3640771338604472</v>
+      </c>
+      <c r="J983">
+        <v>1.18520872200344</v>
+      </c>
+      <c r="K983">
+        <v>4.98</v>
+      </c>
+      <c r="L983">
+        <v>7.45</v>
+      </c>
+      <c r="M983">
+        <v>5.11</v>
+      </c>
+      <c r="N983">
+        <v>7.24</v>
+      </c>
+      <c r="O983">
+        <v>1</v>
+      </c>
+      <c r="P983" t="s">
+        <v>538</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="543">
   <si>
     <t>trade_time</t>
   </si>
@@ -1627,10 +1627,22 @@
     <t>2020-11-05</t>
   </si>
   <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
     <t>2021-09-16</t>
   </si>
   <si>
     <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
+  </si>
+  <si>
+    <t>2021-09-24</t>
+  </si>
+  <si>
+    <t>2021-09-27</t>
   </si>
 </sst>
 </file>
@@ -1988,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P983"/>
+  <dimension ref="A1:P987"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51046,28 +51058,28 @@
         <v>100</v>
       </c>
       <c r="C982">
-        <v>0.7589034565682784</v>
+        <v>0.8361670111513115</v>
       </c>
       <c r="D982" t="s">
         <v>239</v>
       </c>
       <c r="E982">
-        <v>1.042794772534441</v>
+        <v>1.127164759730785</v>
       </c>
       <c r="F982">
         <v>1</v>
       </c>
       <c r="G982">
-        <v>0.01372109654343172</v>
+        <v>0.01364383298884869</v>
       </c>
       <c r="H982">
-        <v>0.01519720522746556</v>
+        <v>0.01511283524026921</v>
       </c>
       <c r="I982">
-        <v>0.2838913159661622</v>
+        <v>0.2909977485794739</v>
       </c>
       <c r="J982">
-        <v>1.268316349008165</v>
+        <v>1.253196279618139</v>
       </c>
       <c r="K982">
         <v>5.11</v>
@@ -51096,28 +51108,28 @@
         <v>100</v>
       </c>
       <c r="C983">
-        <v>0.7508620194677098</v>
+        <v>0.7589034565682784</v>
       </c>
       <c r="D983" t="s">
         <v>239</v>
       </c>
       <c r="E983">
-        <v>1.034013712060629</v>
+        <v>1.042794772534441</v>
       </c>
       <c r="F983">
         <v>1</v>
       </c>
       <c r="G983">
-        <v>0.01372913798053229</v>
+        <v>0.01372109654343172</v>
       </c>
       <c r="H983">
-        <v>0.01520598628793937</v>
+        <v>0.01519720522746556</v>
       </c>
       <c r="I983">
-        <v>0.2831516925929192</v>
+        <v>0.2838913159661622</v>
       </c>
       <c r="J983">
-        <v>1.269890015759744</v>
+        <v>1.268316349008165</v>
       </c>
       <c r="K983">
         <v>5.11</v>
@@ -51136,6 +51148,206 @@
       </c>
       <c r="P983" t="s">
         <v>538</v>
+      </c>
+    </row>
+    <row r="984" spans="1:16">
+      <c r="A984" s="1">
+        <v>0</v>
+      </c>
+      <c r="B984" t="s">
+        <v>100</v>
+      </c>
+      <c r="C984">
+        <v>0.7508620194677098</v>
+      </c>
+      <c r="D984" t="s">
+        <v>239</v>
+      </c>
+      <c r="E984">
+        <v>1.034013712060629</v>
+      </c>
+      <c r="F984">
+        <v>1</v>
+      </c>
+      <c r="G984">
+        <v>0.01372913798053229</v>
+      </c>
+      <c r="H984">
+        <v>0.01520598628793937</v>
+      </c>
+      <c r="I984">
+        <v>0.2831516925929192</v>
+      </c>
+      <c r="J984">
+        <v>1.269890015759744</v>
+      </c>
+      <c r="K984">
+        <v>5.11</v>
+      </c>
+      <c r="L984">
+        <v>7.24</v>
+      </c>
+      <c r="M984">
+        <v>5.58</v>
+      </c>
+      <c r="N984">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="O984">
+        <v>1</v>
+      </c>
+      <c r="P984" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="985" spans="1:16">
+      <c r="A985" s="1">
+        <v>0</v>
+      </c>
+      <c r="B985" t="s">
+        <v>100</v>
+      </c>
+      <c r="C985">
+        <v>0.7598146472136049</v>
+      </c>
+      <c r="D985" t="s">
+        <v>239</v>
+      </c>
+      <c r="E985">
+        <v>1.043789771321314</v>
+      </c>
+      <c r="F985">
+        <v>1</v>
+      </c>
+      <c r="G985">
+        <v>0.01372018535278639</v>
+      </c>
+      <c r="H985">
+        <v>0.01519621022867868</v>
+      </c>
+      <c r="I985">
+        <v>0.2839751241077089</v>
+      </c>
+      <c r="J985">
+        <v>1.268138033813385</v>
+      </c>
+      <c r="K985">
+        <v>5.11</v>
+      </c>
+      <c r="L985">
+        <v>7.24</v>
+      </c>
+      <c r="M985">
+        <v>5.58</v>
+      </c>
+      <c r="N985">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="O985">
+        <v>1</v>
+      </c>
+      <c r="P985" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="986" spans="1:16">
+      <c r="A986" s="1">
+        <v>0</v>
+      </c>
+      <c r="B986" t="s">
+        <v>100</v>
+      </c>
+      <c r="C986">
+        <v>0.7489382777012477</v>
+      </c>
+      <c r="D986" t="s">
+        <v>239</v>
+      </c>
+      <c r="E986">
+        <v>1.031913031227585</v>
+      </c>
+      <c r="F986">
+        <v>1</v>
+      </c>
+      <c r="G986">
+        <v>0.01373106172229875</v>
+      </c>
+      <c r="H986">
+        <v>0.01520808696877241</v>
+      </c>
+      <c r="I986">
+        <v>0.2829747535263376</v>
+      </c>
+      <c r="J986">
+        <v>1.270266481858856</v>
+      </c>
+      <c r="K986">
+        <v>5.11</v>
+      </c>
+      <c r="L986">
+        <v>7.24</v>
+      </c>
+      <c r="M986">
+        <v>5.58</v>
+      </c>
+      <c r="N986">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="O986">
+        <v>1</v>
+      </c>
+      <c r="P986" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="987" spans="1:16">
+      <c r="A987" s="1">
+        <v>0</v>
+      </c>
+      <c r="B987" t="s">
+        <v>100</v>
+      </c>
+      <c r="C987">
+        <v>0.7626869004855017</v>
+      </c>
+      <c r="D987" t="s">
+        <v>239</v>
+      </c>
+      <c r="E987">
+        <v>1.04692620444405</v>
+      </c>
+      <c r="F987">
+        <v>1</v>
+      </c>
+      <c r="G987">
+        <v>0.0137173130995145</v>
+      </c>
+      <c r="H987">
+        <v>0.01519307379555595</v>
+      </c>
+      <c r="I987">
+        <v>0.2842393039585485</v>
+      </c>
+      <c r="J987">
+        <v>1.267575949024364</v>
+      </c>
+      <c r="K987">
+        <v>5.11</v>
+      </c>
+      <c r="L987">
+        <v>7.24</v>
+      </c>
+      <c r="M987">
+        <v>5.58</v>
+      </c>
+      <c r="N987">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="O987">
+        <v>1</v>
+      </c>
+      <c r="P987" t="s">
+        <v>542</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -51220,10 +51220,10 @@
         <v>0.7589034565682784</v>
       </c>
       <c r="D985" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E985">
-        <v>1.042794772534441</v>
+        <v>1.128161099514605</v>
       </c>
       <c r="F985">
         <v>1</v>
@@ -51232,10 +51232,10 @@
         <v>0.01372109654343172</v>
       </c>
       <c r="H985">
-        <v>0.01519720522746556</v>
+        <v>0.0152318389004854</v>
       </c>
       <c r="I985">
-        <v>0.2838913159661622</v>
+        <v>0.3692576429463266</v>
       </c>
       <c r="J985">
         <v>1.268316349008165</v>
@@ -51247,10 +51247,10 @@
         <v>7.24</v>
       </c>
       <c r="M985">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="N985">
-        <v>8.119999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="O985">
         <v>1</v>
@@ -51320,10 +51320,10 @@
         <v>0.7598146472136049</v>
       </c>
       <c r="D987" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E987">
-        <v>1.043789771321314</v>
+        <v>1.129152531997582</v>
       </c>
       <c r="F987">
         <v>1</v>
@@ -51332,10 +51332,10 @@
         <v>0.01372018535278639</v>
       </c>
       <c r="H987">
-        <v>0.01519621022867868</v>
+        <v>0.01523084746800242</v>
       </c>
       <c r="I987">
-        <v>0.2839751241077089</v>
+        <v>0.3693378847839774</v>
       </c>
       <c r="J987">
         <v>1.268138033813385</v>
@@ -51347,10 +51347,10 @@
         <v>7.24</v>
       </c>
       <c r="M987">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="N987">
-        <v>8.119999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="O987">
         <v>1</v>
@@ -51370,10 +51370,10 @@
         <v>0.7489382777012477</v>
       </c>
       <c r="D988" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E988">
-        <v>1.031913031227585</v>
+        <v>1.117318360864763</v>
       </c>
       <c r="F988">
         <v>1</v>
@@ -51382,10 +51382,10 @@
         <v>0.01373106172229875</v>
       </c>
       <c r="H988">
-        <v>0.01520808696877241</v>
+        <v>0.01524268163913524</v>
       </c>
       <c r="I988">
-        <v>0.2829747535263376</v>
+        <v>0.3683800831635153</v>
       </c>
       <c r="J988">
         <v>1.270266481858856</v>
@@ -51397,10 +51397,10 @@
         <v>7.24</v>
       </c>
       <c r="M988">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="N988">
-        <v>8.119999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="O988">
         <v>1</v>
@@ -51420,10 +51420,10 @@
         <v>0.7626869004855017</v>
       </c>
       <c r="D989" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E989">
-        <v>1.04692620444405</v>
+        <v>1.132277723424538</v>
       </c>
       <c r="F989">
         <v>1</v>
@@ -51432,10 +51432,10 @@
         <v>0.0137173130995145</v>
       </c>
       <c r="H989">
-        <v>0.01519307379555595</v>
+        <v>0.01522772227657546</v>
       </c>
       <c r="I989">
-        <v>0.2842393039585485</v>
+        <v>0.3695908229390366</v>
       </c>
       <c r="J989">
         <v>1.267575949024364</v>
@@ -51447,10 +51447,10 @@
         <v>7.24</v>
       </c>
       <c r="M989">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="N989">
-        <v>8.119999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="O989">
         <v>1</v>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2979" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2988" uniqueCount="548">
   <si>
     <t>trade_time</t>
   </si>
@@ -1634,6 +1634,12 @@
   </si>
   <si>
     <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>2021-09-09</t>
+  </si>
+  <si>
+    <t>2021-09-10</t>
   </si>
   <si>
     <t>2021-09-13</t>
@@ -2009,7 +2015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P989"/>
+  <dimension ref="A1:P992"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51067,28 +51073,28 @@
         <v>100</v>
       </c>
       <c r="C982">
-        <v>1.026005428785806</v>
+        <v>1.122991524489409</v>
       </c>
       <c r="D982" t="s">
         <v>240</v>
       </c>
       <c r="E982">
-        <v>1.410675729355167</v>
+        <v>1.503737532169028</v>
       </c>
       <c r="F982">
         <v>1</v>
       </c>
       <c r="G982">
-        <v>0.01361399457121419</v>
+        <v>0.01351700847551059</v>
       </c>
       <c r="H982">
-        <v>0.01348932427064483</v>
+        <v>0.01339626246783097</v>
       </c>
       <c r="I982">
-        <v>0.3846703005693604</v>
+        <v>0.380746007679619</v>
       </c>
       <c r="J982">
-        <v>1.212715716996954</v>
+        <v>1.194028607998187</v>
       </c>
       <c r="K982">
         <v>5.19</v>
@@ -51114,49 +51120,49 @@
         <v>0</v>
       </c>
       <c r="B983" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C983">
-        <v>0.9372250400575854</v>
+        <v>1.09631309962875</v>
       </c>
       <c r="D983" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E983">
-        <v>1.237517754113761</v>
+        <v>1.478138581146662</v>
       </c>
       <c r="F983">
         <v>1</v>
       </c>
       <c r="G983">
-        <v>0.01354277495994242</v>
+        <v>0.01354368690037125</v>
       </c>
       <c r="H983">
-        <v>0.01500248224588624</v>
+        <v>0.01342186141885334</v>
       </c>
       <c r="I983">
-        <v>0.3002927140561757</v>
+        <v>0.3818254815179118</v>
       </c>
       <c r="J983">
-        <v>1.233419757327283</v>
+        <v>1.199168959609104</v>
       </c>
       <c r="K983">
-        <v>5.11</v>
+        <v>5.19</v>
       </c>
       <c r="L983">
-        <v>7.24</v>
+        <v>7.32</v>
       </c>
       <c r="M983">
-        <v>5.58</v>
+        <v>4.98</v>
       </c>
       <c r="N983">
-        <v>8.119999999999999</v>
+        <v>7.45</v>
       </c>
       <c r="O983">
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>100</v>
+        <v>541</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51164,81 +51170,81 @@
         <v>0</v>
       </c>
       <c r="B984" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C984">
-        <v>0.8361670111513115</v>
+        <v>1.026005428785806</v>
       </c>
       <c r="D984" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E984">
-        <v>1.127164759730785</v>
+        <v>1.410675729355167</v>
       </c>
       <c r="F984">
         <v>1</v>
       </c>
       <c r="G984">
-        <v>0.01364383298884869</v>
+        <v>0.01361399457121419</v>
       </c>
       <c r="H984">
-        <v>0.01511283524026921</v>
+        <v>0.01348932427064483</v>
       </c>
       <c r="I984">
-        <v>0.2909977485794739</v>
+        <v>0.3846703005693604</v>
       </c>
       <c r="J984">
-        <v>1.253196279618139</v>
+        <v>1.212715716996954</v>
       </c>
       <c r="K984">
-        <v>5.11</v>
+        <v>5.19</v>
       </c>
       <c r="L984">
-        <v>7.24</v>
+        <v>7.32</v>
       </c>
       <c r="M984">
-        <v>5.58</v>
+        <v>4.98</v>
       </c>
       <c r="N984">
-        <v>8.119999999999999</v>
+        <v>7.45</v>
       </c>
       <c r="O984">
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="985" spans="1:16">
       <c r="A985" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B985" t="s">
         <v>101</v>
       </c>
       <c r="C985">
-        <v>0.7589034565682784</v>
+        <v>1.043022686145562</v>
       </c>
       <c r="D985" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E985">
-        <v>1.128161099514605</v>
+        <v>1.353046299156993</v>
       </c>
       <c r="F985">
         <v>1</v>
       </c>
       <c r="G985">
-        <v>0.01372109654343172</v>
+        <v>0.01343697731385444</v>
       </c>
       <c r="H985">
-        <v>0.0152318389004854</v>
+        <v>0.014886953700843</v>
       </c>
       <c r="I985">
-        <v>0.3692576429463266</v>
+        <v>0.3100236130114311</v>
       </c>
       <c r="J985">
-        <v>1.268316349008165</v>
+        <v>1.212715716996954</v>
       </c>
       <c r="K985">
         <v>5.11</v>
@@ -51247,10 +51253,10 @@
         <v>7.24</v>
       </c>
       <c r="M985">
-        <v>5.56</v>
+        <v>5.58</v>
       </c>
       <c r="N985">
-        <v>8.18</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="O985">
         <v>1</v>
@@ -51267,28 +51273,28 @@
         <v>101</v>
       </c>
       <c r="C986">
-        <v>0.7508620194677098</v>
+        <v>0.9372250400575854</v>
       </c>
       <c r="D986" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E986">
-        <v>1.119411512375826</v>
+        <v>1.237517754113761</v>
       </c>
       <c r="F986">
         <v>1</v>
       </c>
       <c r="G986">
-        <v>0.01372913798053229</v>
+        <v>0.01354277495994242</v>
       </c>
       <c r="H986">
-        <v>0.01524058848762417</v>
+        <v>0.01500248224588624</v>
       </c>
       <c r="I986">
-        <v>0.3685494929081159</v>
+        <v>0.3002927140561757</v>
       </c>
       <c r="J986">
-        <v>1.269890015759744</v>
+        <v>1.233419757327283</v>
       </c>
       <c r="K986">
         <v>5.11</v>
@@ -51297,16 +51303,16 @@
         <v>7.24</v>
       </c>
       <c r="M986">
-        <v>5.56</v>
+        <v>5.58</v>
       </c>
       <c r="N986">
-        <v>8.18</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="O986">
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>240</v>
+        <v>100</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51317,28 +51323,28 @@
         <v>101</v>
       </c>
       <c r="C987">
-        <v>0.7598146472136049</v>
+        <v>0.8361670111513115</v>
       </c>
       <c r="D987" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E987">
-        <v>1.129152531997582</v>
+        <v>1.127164759730785</v>
       </c>
       <c r="F987">
         <v>1</v>
       </c>
       <c r="G987">
-        <v>0.01372018535278639</v>
+        <v>0.01364383298884869</v>
       </c>
       <c r="H987">
-        <v>0.01523084746800242</v>
+        <v>0.01511283524026921</v>
       </c>
       <c r="I987">
-        <v>0.3693378847839774</v>
+        <v>0.2909977485794739</v>
       </c>
       <c r="J987">
-        <v>1.268138033813385</v>
+        <v>1.253196279618139</v>
       </c>
       <c r="K987">
         <v>5.11</v>
@@ -51347,10 +51353,10 @@
         <v>7.24</v>
       </c>
       <c r="M987">
-        <v>5.56</v>
+        <v>5.58</v>
       </c>
       <c r="N987">
-        <v>8.18</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="O987">
         <v>1</v>
@@ -51367,28 +51373,28 @@
         <v>101</v>
       </c>
       <c r="C988">
-        <v>0.7489382777012477</v>
+        <v>0.7589034565682784</v>
       </c>
       <c r="D988" t="s">
         <v>242</v>
       </c>
       <c r="E988">
-        <v>1.117318360864763</v>
+        <v>1.128161099514605</v>
       </c>
       <c r="F988">
         <v>1</v>
       </c>
       <c r="G988">
-        <v>0.01373106172229875</v>
+        <v>0.01372109654343172</v>
       </c>
       <c r="H988">
-        <v>0.01524268163913524</v>
+        <v>0.0152318389004854</v>
       </c>
       <c r="I988">
-        <v>0.3683800831635153</v>
+        <v>0.3692576429463266</v>
       </c>
       <c r="J988">
-        <v>1.270266481858856</v>
+        <v>1.268316349008165</v>
       </c>
       <c r="K988">
         <v>5.11</v>
@@ -51417,28 +51423,28 @@
         <v>101</v>
       </c>
       <c r="C989">
-        <v>0.7626869004855017</v>
+        <v>0.7508620194677098</v>
       </c>
       <c r="D989" t="s">
         <v>242</v>
       </c>
       <c r="E989">
-        <v>1.132277723424538</v>
+        <v>1.119411512375826</v>
       </c>
       <c r="F989">
         <v>1</v>
       </c>
       <c r="G989">
-        <v>0.0137173130995145</v>
+        <v>0.01372913798053229</v>
       </c>
       <c r="H989">
-        <v>0.01522772227657546</v>
+        <v>0.01524058848762417</v>
       </c>
       <c r="I989">
-        <v>0.3695908229390366</v>
+        <v>0.3685494929081159</v>
       </c>
       <c r="J989">
-        <v>1.267575949024364</v>
+        <v>1.269890015759744</v>
       </c>
       <c r="K989">
         <v>5.11</v>
@@ -51456,7 +51462,157 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="990" spans="1:16">
+      <c r="A990" s="1">
+        <v>0</v>
+      </c>
+      <c r="B990" t="s">
+        <v>101</v>
+      </c>
+      <c r="C990">
+        <v>0.7598146472136049</v>
+      </c>
+      <c r="D990" t="s">
+        <v>242</v>
+      </c>
+      <c r="E990">
+        <v>1.129152531997582</v>
+      </c>
+      <c r="F990">
+        <v>1</v>
+      </c>
+      <c r="G990">
+        <v>0.01372018535278639</v>
+      </c>
+      <c r="H990">
+        <v>0.01523084746800242</v>
+      </c>
+      <c r="I990">
+        <v>0.3693378847839774</v>
+      </c>
+      <c r="J990">
+        <v>1.268138033813385</v>
+      </c>
+      <c r="K990">
+        <v>5.11</v>
+      </c>
+      <c r="L990">
+        <v>7.24</v>
+      </c>
+      <c r="M990">
+        <v>5.56</v>
+      </c>
+      <c r="N990">
+        <v>8.18</v>
+      </c>
+      <c r="O990">
+        <v>1</v>
+      </c>
+      <c r="P990" t="s">
         <v>545</v>
+      </c>
+    </row>
+    <row r="991" spans="1:16">
+      <c r="A991" s="1">
+        <v>0</v>
+      </c>
+      <c r="B991" t="s">
+        <v>101</v>
+      </c>
+      <c r="C991">
+        <v>0.7489382777012477</v>
+      </c>
+      <c r="D991" t="s">
+        <v>242</v>
+      </c>
+      <c r="E991">
+        <v>1.117318360864763</v>
+      </c>
+      <c r="F991">
+        <v>1</v>
+      </c>
+      <c r="G991">
+        <v>0.01373106172229875</v>
+      </c>
+      <c r="H991">
+        <v>0.01524268163913524</v>
+      </c>
+      <c r="I991">
+        <v>0.3683800831635153</v>
+      </c>
+      <c r="J991">
+        <v>1.270266481858856</v>
+      </c>
+      <c r="K991">
+        <v>5.11</v>
+      </c>
+      <c r="L991">
+        <v>7.24</v>
+      </c>
+      <c r="M991">
+        <v>5.56</v>
+      </c>
+      <c r="N991">
+        <v>8.18</v>
+      </c>
+      <c r="O991">
+        <v>1</v>
+      </c>
+      <c r="P991" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="992" spans="1:16">
+      <c r="A992" s="1">
+        <v>0</v>
+      </c>
+      <c r="B992" t="s">
+        <v>101</v>
+      </c>
+      <c r="C992">
+        <v>0.7626869004855017</v>
+      </c>
+      <c r="D992" t="s">
+        <v>242</v>
+      </c>
+      <c r="E992">
+        <v>1.132277723424538</v>
+      </c>
+      <c r="F992">
+        <v>1</v>
+      </c>
+      <c r="G992">
+        <v>0.0137173130995145</v>
+      </c>
+      <c r="H992">
+        <v>0.01522772227657546</v>
+      </c>
+      <c r="I992">
+        <v>0.3695908229390366</v>
+      </c>
+      <c r="J992">
+        <v>1.267575949024364</v>
+      </c>
+      <c r="K992">
+        <v>5.11</v>
+      </c>
+      <c r="L992">
+        <v>7.24</v>
+      </c>
+      <c r="M992">
+        <v>5.56</v>
+      </c>
+      <c r="N992">
+        <v>8.18</v>
+      </c>
+      <c r="O992">
+        <v>1</v>
+      </c>
+      <c r="P992" t="s">
+        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3000" uniqueCount="552">
   <si>
     <t>trade_time</t>
   </si>
@@ -316,7 +316,7 @@
     <t>2021-03-22</t>
   </si>
   <si>
-    <t>2021-11-02</t>
+    <t>2021-11-08</t>
   </si>
   <si>
     <t>2016-12-12</t>
@@ -733,7 +733,7 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-11-08</t>
+    <t>2021-11-09</t>
   </si>
   <si>
     <t>2016-10-31</t>
@@ -1637,6 +1637,39 @@
   </si>
   <si>
     <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>2021-09-09</t>
+  </si>
+  <si>
+    <t>2021-09-10</t>
+  </si>
+  <si>
+    <t>2021-09-13</t>
+  </si>
+  <si>
+    <t>2021-09-14</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
+  </si>
+  <si>
+    <t>2021-09-16</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
+  </si>
+  <si>
+    <t>2021-09-24</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P985"/>
+  <dimension ref="A1:P996"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51052,40 +51085,40 @@
         <v>100</v>
       </c>
       <c r="C982">
-        <v>2.486803581069362</v>
+        <v>2.666234305352259</v>
       </c>
       <c r="D982" t="s">
         <v>239</v>
       </c>
       <c r="E982">
-        <v>2.666234305352259</v>
+        <v>2.536091986422985</v>
       </c>
       <c r="F982">
         <v>-1</v>
       </c>
       <c r="G982">
-        <v>0.01445319641893064</v>
+        <v>0.01535376569464774</v>
       </c>
       <c r="H982">
-        <v>0.01535376569464774</v>
+        <v>0.01540390801357702</v>
       </c>
       <c r="I982">
-        <v>-0.1794307242828976</v>
+        <v>0.1301423189292743</v>
       </c>
       <c r="J982">
         <v>1.12677898661594</v>
       </c>
       <c r="K982">
-        <v>5.31</v>
+        <v>5.63</v>
       </c>
       <c r="L982">
-        <v>8.470000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="M982">
-        <v>5.63</v>
+        <v>5.71</v>
       </c>
       <c r="N982">
-        <v>9.01</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O982">
         <v>1</v>
@@ -51102,40 +51135,40 @@
         <v>100</v>
       </c>
       <c r="C983">
-        <v>2.404176087352699</v>
+        <v>2.578627376986005</v>
       </c>
       <c r="D983" t="s">
         <v>239</v>
       </c>
       <c r="E983">
-        <v>2.578627376986005</v>
+        <v>2.447240199394333</v>
       </c>
       <c r="F983">
         <v>-1</v>
       </c>
       <c r="G983">
-        <v>0.0145358239126473</v>
+        <v>0.01544137262301399</v>
       </c>
       <c r="H983">
-        <v>0.01544137262301399</v>
+        <v>0.01549275980060567</v>
       </c>
       <c r="I983">
-        <v>-0.1744512896333061</v>
+        <v>0.1313871775916722</v>
       </c>
       <c r="J983">
         <v>1.142339719895914</v>
       </c>
       <c r="K983">
-        <v>5.31</v>
+        <v>5.63</v>
       </c>
       <c r="L983">
-        <v>8.470000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="M983">
-        <v>5.63</v>
+        <v>5.71</v>
       </c>
       <c r="N983">
-        <v>9.01</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O983">
         <v>1</v>
@@ -51152,40 +51185,40 @@
         <v>100</v>
       </c>
       <c r="C984">
-        <v>2.242073332981041</v>
+        <v>2.406755718396094</v>
       </c>
       <c r="D984" t="s">
         <v>239</v>
       </c>
       <c r="E984">
-        <v>2.406755718396094</v>
+        <v>2.272926314749858</v>
       </c>
       <c r="F984">
         <v>-1</v>
       </c>
       <c r="G984">
-        <v>0.01469792666701896</v>
+        <v>0.01561324428160391</v>
       </c>
       <c r="H984">
-        <v>0.01561324428160391</v>
+        <v>0.01566707368525014</v>
       </c>
       <c r="I984">
-        <v>-0.1646823854150528</v>
+        <v>0.133829403646236</v>
       </c>
       <c r="J984">
         <v>1.172867545577958</v>
       </c>
       <c r="K984">
-        <v>5.31</v>
+        <v>5.63</v>
       </c>
       <c r="L984">
-        <v>8.470000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="M984">
-        <v>5.63</v>
+        <v>5.71</v>
       </c>
       <c r="N984">
-        <v>9.01</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O984">
         <v>1</v>
@@ -51202,46 +51235,596 @@
         <v>100</v>
       </c>
       <c r="C985">
-        <v>2.176541686161737</v>
+        <v>2.337274895120635</v>
       </c>
       <c r="D985" t="s">
         <v>239</v>
       </c>
       <c r="E985">
-        <v>2.337274895120635</v>
+        <v>2.202458197360361</v>
       </c>
       <c r="F985">
         <v>-1</v>
       </c>
       <c r="G985">
-        <v>0.01476345831383826</v>
+        <v>0.01568272510487936</v>
       </c>
       <c r="H985">
-        <v>0.01568272510487936</v>
+        <v>0.01573754180263964</v>
       </c>
       <c r="I985">
-        <v>-0.1607332089588978</v>
+        <v>0.1348166977602743</v>
       </c>
       <c r="J985">
         <v>1.18520872200344</v>
       </c>
       <c r="K985">
-        <v>5.31</v>
+        <v>5.63</v>
       </c>
       <c r="L985">
-        <v>8.470000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="M985">
-        <v>5.63</v>
+        <v>5.71</v>
       </c>
       <c r="N985">
-        <v>9.01</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="O985">
         <v>1</v>
       </c>
       <c r="P985" t="s">
         <v>540</v>
+      </c>
+    </row>
+    <row r="986" spans="1:16">
+      <c r="A986" s="1">
+        <v>0</v>
+      </c>
+      <c r="B986" t="s">
+        <v>100</v>
+      </c>
+      <c r="C986">
+        <v>2.319744863311787</v>
+      </c>
+      <c r="D986" t="s">
+        <v>239</v>
+      </c>
+      <c r="E986">
+        <v>2.184679070960978</v>
+      </c>
+      <c r="F986">
+        <v>-1</v>
+      </c>
+      <c r="G986">
+        <v>0.01570025513668821</v>
+      </c>
+      <c r="H986">
+        <v>0.01575532092903902</v>
+      </c>
+      <c r="I986">
+        <v>0.135065792350809</v>
+      </c>
+      <c r="J986">
+        <v>1.188322404385118</v>
+      </c>
+      <c r="K986">
+        <v>5.63</v>
+      </c>
+      <c r="L986">
+        <v>9.01</v>
+      </c>
+      <c r="M986">
+        <v>5.71</v>
+      </c>
+      <c r="N986">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O986">
+        <v>1</v>
+      </c>
+      <c r="P986" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="987" spans="1:16">
+      <c r="A987" s="1">
+        <v>0</v>
+      </c>
+      <c r="B987" t="s">
+        <v>100</v>
+      </c>
+      <c r="C987">
+        <v>2.310700701204147</v>
+      </c>
+      <c r="D987" t="s">
+        <v>239</v>
+      </c>
+      <c r="E987">
+        <v>2.175506395004562</v>
+      </c>
+      <c r="F987">
+        <v>-1</v>
+      </c>
+      <c r="G987">
+        <v>0.01570929929879585</v>
+      </c>
+      <c r="H987">
+        <v>0.01576449360499544</v>
+      </c>
+      <c r="I987">
+        <v>0.1351943061995851</v>
+      </c>
+      <c r="J987">
+        <v>1.189928827494823</v>
+      </c>
+      <c r="K987">
+        <v>5.63</v>
+      </c>
+      <c r="L987">
+        <v>9.01</v>
+      </c>
+      <c r="M987">
+        <v>5.71</v>
+      </c>
+      <c r="N987">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O987">
+        <v>1</v>
+      </c>
+      <c r="P987" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="988" spans="1:16">
+      <c r="A988" s="1">
+        <v>0</v>
+      </c>
+      <c r="B988" t="s">
+        <v>100</v>
+      </c>
+      <c r="C988">
+        <v>2.287618936970207</v>
+      </c>
+      <c r="D988" t="s">
+        <v>239</v>
+      </c>
+      <c r="E988">
+        <v>2.152096648330353</v>
+      </c>
+      <c r="F988">
+        <v>-1</v>
+      </c>
+      <c r="G988">
+        <v>0.01573238106302979</v>
+      </c>
+      <c r="H988">
+        <v>0.01578790335166965</v>
+      </c>
+      <c r="I988">
+        <v>0.1355222886398542</v>
+      </c>
+      <c r="J988">
+        <v>1.194028607998187</v>
+      </c>
+      <c r="K988">
+        <v>5.63</v>
+      </c>
+      <c r="L988">
+        <v>9.01</v>
+      </c>
+      <c r="M988">
+        <v>5.71</v>
+      </c>
+      <c r="N988">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O988">
+        <v>1</v>
+      </c>
+      <c r="P988" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="989" spans="1:16">
+      <c r="A989" s="1">
+        <v>0</v>
+      </c>
+      <c r="B989" t="s">
+        <v>100</v>
+      </c>
+      <c r="C989">
+        <v>2.258678757400745</v>
+      </c>
+      <c r="D989" t="s">
+        <v>239</v>
+      </c>
+      <c r="E989">
+        <v>2.122745240632017</v>
+      </c>
+      <c r="F989">
+        <v>-1</v>
+      </c>
+      <c r="G989">
+        <v>0.01576132124259925</v>
+      </c>
+      <c r="H989">
+        <v>0.01581725475936798</v>
+      </c>
+      <c r="I989">
+        <v>0.1359335167687279</v>
+      </c>
+      <c r="J989">
+        <v>1.199168959609104</v>
+      </c>
+      <c r="K989">
+        <v>5.63</v>
+      </c>
+      <c r="L989">
+        <v>9.01</v>
+      </c>
+      <c r="M989">
+        <v>5.71</v>
+      </c>
+      <c r="N989">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O989">
+        <v>1</v>
+      </c>
+      <c r="P989" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="990" spans="1:16">
+      <c r="A990" s="1">
+        <v>0</v>
+      </c>
+      <c r="B990" t="s">
+        <v>100</v>
+      </c>
+      <c r="C990">
+        <v>2.182410513307146</v>
+      </c>
+      <c r="D990" t="s">
+        <v>239</v>
+      </c>
+      <c r="E990">
+        <v>2.045393255947391</v>
+      </c>
+      <c r="F990">
+        <v>-1</v>
+      </c>
+      <c r="G990">
+        <v>0.01583758948669285</v>
+      </c>
+      <c r="H990">
+        <v>0.01589460674405261</v>
+      </c>
+      <c r="I990">
+        <v>0.137017257359755</v>
+      </c>
+      <c r="J990">
+        <v>1.212715716996954</v>
+      </c>
+      <c r="K990">
+        <v>5.63</v>
+      </c>
+      <c r="L990">
+        <v>9.01</v>
+      </c>
+      <c r="M990">
+        <v>5.71</v>
+      </c>
+      <c r="N990">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O990">
+        <v>1</v>
+      </c>
+      <c r="P990" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="991" spans="1:16">
+      <c r="A991" s="1">
+        <v>0</v>
+      </c>
+      <c r="B991" t="s">
+        <v>100</v>
+      </c>
+      <c r="C991">
+        <v>2.065846766247398</v>
+      </c>
+      <c r="D991" t="s">
+        <v>239</v>
+      </c>
+      <c r="E991">
+        <v>1.927173185661217</v>
+      </c>
+      <c r="F991">
+        <v>-1</v>
+      </c>
+      <c r="G991">
+        <v>0.0159541532337526</v>
+      </c>
+      <c r="H991">
+        <v>0.01601282681433878</v>
+      </c>
+      <c r="I991">
+        <v>0.1386735805861816</v>
+      </c>
+      <c r="J991">
+        <v>1.233419757327283</v>
+      </c>
+      <c r="K991">
+        <v>5.63</v>
+      </c>
+      <c r="L991">
+        <v>9.01</v>
+      </c>
+      <c r="M991">
+        <v>5.71</v>
+      </c>
+      <c r="N991">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O991">
+        <v>1</v>
+      </c>
+      <c r="P991" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="992" spans="1:16">
+      <c r="A992" s="1">
+        <v>0</v>
+      </c>
+      <c r="B992" t="s">
+        <v>100</v>
+      </c>
+      <c r="C992">
+        <v>1.954504945749879</v>
+      </c>
+      <c r="D992" t="s">
+        <v>239</v>
+      </c>
+      <c r="E992">
+        <v>1.814249243380429</v>
+      </c>
+      <c r="F992">
+        <v>-1</v>
+      </c>
+      <c r="G992">
+        <v>0.01606549505425012</v>
+      </c>
+      <c r="H992">
+        <v>0.01612575075661957</v>
+      </c>
+      <c r="I992">
+        <v>0.1402557023694504</v>
+      </c>
+      <c r="J992">
+        <v>1.253196279618139</v>
+      </c>
+      <c r="K992">
+        <v>5.63</v>
+      </c>
+      <c r="L992">
+        <v>9.01</v>
+      </c>
+      <c r="M992">
+        <v>5.71</v>
+      </c>
+      <c r="N992">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O992">
+        <v>1</v>
+      </c>
+      <c r="P992" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="993" spans="1:16">
+      <c r="A993" s="1">
+        <v>0</v>
+      </c>
+      <c r="B993" t="s">
+        <v>100</v>
+      </c>
+      <c r="C993">
+        <v>1.869378955084033</v>
+      </c>
+      <c r="D993" t="s">
+        <v>239</v>
+      </c>
+      <c r="E993">
+        <v>1.727913647163381</v>
+      </c>
+      <c r="F993">
+        <v>-1</v>
+      </c>
+      <c r="G993">
+        <v>0.01615062104491597</v>
+      </c>
+      <c r="H993">
+        <v>0.01621208635283662</v>
+      </c>
+      <c r="I993">
+        <v>0.1414653079206527</v>
+      </c>
+      <c r="J993">
+        <v>1.268316349008165</v>
+      </c>
+      <c r="K993">
+        <v>5.63</v>
+      </c>
+      <c r="L993">
+        <v>9.01</v>
+      </c>
+      <c r="M993">
+        <v>5.71</v>
+      </c>
+      <c r="N993">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O993">
+        <v>1</v>
+      </c>
+      <c r="P993" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="994" spans="1:16">
+      <c r="A994" s="1">
+        <v>0</v>
+      </c>
+      <c r="B994" t="s">
+        <v>100</v>
+      </c>
+      <c r="C994">
+        <v>1.860519211272643</v>
+      </c>
+      <c r="D994" t="s">
+        <v>239</v>
+      </c>
+      <c r="E994">
+        <v>1.718928010011864</v>
+      </c>
+      <c r="F994">
+        <v>-1</v>
+      </c>
+      <c r="G994">
+        <v>0.01615948078872736</v>
+      </c>
+      <c r="H994">
+        <v>0.01622107198998814</v>
+      </c>
+      <c r="I994">
+        <v>0.1415912012607787</v>
+      </c>
+      <c r="J994">
+        <v>1.269890015759744</v>
+      </c>
+      <c r="K994">
+        <v>5.63</v>
+      </c>
+      <c r="L994">
+        <v>9.01</v>
+      </c>
+      <c r="M994">
+        <v>5.71</v>
+      </c>
+      <c r="N994">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O994">
+        <v>1</v>
+      </c>
+      <c r="P994" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="995" spans="1:16">
+      <c r="A995" s="1">
+        <v>0</v>
+      </c>
+      <c r="B995" t="s">
+        <v>100</v>
+      </c>
+      <c r="C995">
+        <v>1.870382869630645</v>
+      </c>
+      <c r="D995" t="s">
+        <v>239</v>
+      </c>
+      <c r="E995">
+        <v>1.728931826925575</v>
+      </c>
+      <c r="F995">
+        <v>-1</v>
+      </c>
+      <c r="G995">
+        <v>0.01614961713036935</v>
+      </c>
+      <c r="H995">
+        <v>0.01621106817307443</v>
+      </c>
+      <c r="I995">
+        <v>0.1414510427050697</v>
+      </c>
+      <c r="J995">
+        <v>1.268138033813385</v>
+      </c>
+      <c r="K995">
+        <v>5.63</v>
+      </c>
+      <c r="L995">
+        <v>9.01</v>
+      </c>
+      <c r="M995">
+        <v>5.71</v>
+      </c>
+      <c r="N995">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O995">
+        <v>1</v>
+      </c>
+      <c r="P995" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="996" spans="1:16">
+      <c r="A996" s="1">
+        <v>0</v>
+      </c>
+      <c r="B996" t="s">
+        <v>100</v>
+      </c>
+      <c r="C996">
+        <v>1.858399707134643</v>
+      </c>
+      <c r="D996" t="s">
+        <v>239</v>
+      </c>
+      <c r="E996">
+        <v>1.716778388585936</v>
+      </c>
+      <c r="F996">
+        <v>-1</v>
+      </c>
+      <c r="G996">
+        <v>0.01616160029286536</v>
+      </c>
+      <c r="H996">
+        <v>0.01622322161141406</v>
+      </c>
+      <c r="I996">
+        <v>0.1416213185487072</v>
+      </c>
+      <c r="J996">
+        <v>1.270266481858856</v>
+      </c>
+      <c r="K996">
+        <v>5.63</v>
+      </c>
+      <c r="L996">
+        <v>9.01</v>
+      </c>
+      <c r="M996">
+        <v>5.71</v>
+      </c>
+      <c r="N996">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="O996">
+        <v>1</v>
+      </c>
+      <c r="P996" t="s">
+        <v>551</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -733,7 +733,7 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-11-09</t>
+    <t>2021-11-10</t>
   </si>
   <si>
     <t>2016-10-31</t>
@@ -51091,7 +51091,7 @@
         <v>239</v>
       </c>
       <c r="E982">
-        <v>2.536091986422985</v>
+        <v>2.281163145887622</v>
       </c>
       <c r="F982">
         <v>-1</v>
@@ -51100,10 +51100,10 @@
         <v>0.01535376569464774</v>
       </c>
       <c r="H982">
-        <v>0.01540390801357702</v>
+        <v>0.01505883685411238</v>
       </c>
       <c r="I982">
-        <v>0.1301423189292743</v>
+        <v>0.385071159464637</v>
       </c>
       <c r="J982">
         <v>1.12677898661594</v>
@@ -51115,10 +51115,10 @@
         <v>9.01</v>
       </c>
       <c r="M982">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N982">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O982">
         <v>1</v>
@@ -51141,7 +51141,7 @@
         <v>239</v>
       </c>
       <c r="E983">
-        <v>2.447240199394333</v>
+        <v>2.192933788190169</v>
       </c>
       <c r="F983">
         <v>-1</v>
@@ -51150,10 +51150,10 @@
         <v>0.01544137262301399</v>
       </c>
       <c r="H983">
-        <v>0.01549275980060567</v>
+        <v>0.01514706621180983</v>
       </c>
       <c r="I983">
-        <v>0.1313871775916722</v>
+        <v>0.3856935887958359</v>
       </c>
       <c r="J983">
         <v>1.142339719895914</v>
@@ -51165,10 +51165,10 @@
         <v>9.01</v>
       </c>
       <c r="M983">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N983">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O983">
         <v>1</v>
@@ -51191,7 +51191,7 @@
         <v>239</v>
       </c>
       <c r="E984">
-        <v>2.272926314749858</v>
+        <v>2.019841016572975</v>
       </c>
       <c r="F984">
         <v>-1</v>
@@ -51200,10 +51200,10 @@
         <v>0.01561324428160391</v>
       </c>
       <c r="H984">
-        <v>0.01566707368525014</v>
+        <v>0.01532015898342702</v>
       </c>
       <c r="I984">
-        <v>0.133829403646236</v>
+        <v>0.3869147018231187</v>
       </c>
       <c r="J984">
         <v>1.172867545577958</v>
@@ -51215,10 +51215,10 @@
         <v>9.01</v>
       </c>
       <c r="M984">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N984">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O984">
         <v>1</v>
@@ -51241,7 +51241,7 @@
         <v>239</v>
       </c>
       <c r="E985">
-        <v>2.202458197360361</v>
+        <v>1.949866546240498</v>
       </c>
       <c r="F985">
         <v>-1</v>
@@ -51250,10 +51250,10 @@
         <v>0.01568272510487936</v>
       </c>
       <c r="H985">
-        <v>0.01573754180263964</v>
+        <v>0.0153901334537595</v>
       </c>
       <c r="I985">
-        <v>0.1348166977602743</v>
+        <v>0.387408348880137</v>
       </c>
       <c r="J985">
         <v>1.18520872200344</v>
@@ -51265,10 +51265,10 @@
         <v>9.01</v>
       </c>
       <c r="M985">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N985">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O985">
         <v>1</v>
@@ -51291,7 +51291,7 @@
         <v>239</v>
       </c>
       <c r="E986">
-        <v>2.184679070960978</v>
+        <v>1.932211967136382</v>
       </c>
       <c r="F986">
         <v>-1</v>
@@ -51300,10 +51300,10 @@
         <v>0.01570025513668821</v>
       </c>
       <c r="H986">
-        <v>0.01575532092903902</v>
+        <v>0.01540778803286362</v>
       </c>
       <c r="I986">
-        <v>0.135065792350809</v>
+        <v>0.3875328961754052</v>
       </c>
       <c r="J986">
         <v>1.188322404385118</v>
@@ -51315,10 +51315,10 @@
         <v>9.01</v>
       </c>
       <c r="M986">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N986">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O986">
         <v>1</v>
@@ -51341,7 +51341,7 @@
         <v>239</v>
       </c>
       <c r="E987">
-        <v>2.175506395004562</v>
+        <v>1.923103548104354</v>
       </c>
       <c r="F987">
         <v>-1</v>
@@ -51350,10 +51350,10 @@
         <v>0.01570929929879585</v>
       </c>
       <c r="H987">
-        <v>0.01576449360499544</v>
+        <v>0.01541689645189565</v>
       </c>
       <c r="I987">
-        <v>0.1351943061995851</v>
+        <v>0.3875971530997928</v>
       </c>
       <c r="J987">
         <v>1.189928827494823</v>
@@ -51365,10 +51365,10 @@
         <v>9.01</v>
       </c>
       <c r="M987">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N987">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O987">
         <v>1</v>
@@ -51391,7 +51391,7 @@
         <v>239</v>
       </c>
       <c r="E988">
-        <v>2.152096648330353</v>
+        <v>1.89985779265028</v>
       </c>
       <c r="F988">
         <v>-1</v>
@@ -51400,10 +51400,10 @@
         <v>0.01573238106302979</v>
       </c>
       <c r="H988">
-        <v>0.01578790335166965</v>
+        <v>0.01544014220734972</v>
       </c>
       <c r="I988">
-        <v>0.1355222886398542</v>
+        <v>0.3877611443199278</v>
       </c>
       <c r="J988">
         <v>1.194028607998187</v>
@@ -51415,10 +51415,10 @@
         <v>9.01</v>
       </c>
       <c r="M988">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N988">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O988">
         <v>1</v>
@@ -51441,7 +51441,7 @@
         <v>239</v>
       </c>
       <c r="E989">
-        <v>2.122745240632017</v>
+        <v>1.870711999016381</v>
       </c>
       <c r="F989">
         <v>-1</v>
@@ -51450,10 +51450,10 @@
         <v>0.01576132124259925</v>
       </c>
       <c r="H989">
-        <v>0.01581725475936798</v>
+        <v>0.01546928800098362</v>
       </c>
       <c r="I989">
-        <v>0.1359335167687279</v>
+        <v>0.3879667583843638</v>
       </c>
       <c r="J989">
         <v>1.199168959609104</v>
@@ -51465,10 +51465,10 @@
         <v>9.01</v>
       </c>
       <c r="M989">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N989">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O989">
         <v>1</v>
@@ -51491,7 +51491,7 @@
         <v>239</v>
       </c>
       <c r="E990">
-        <v>2.045393255947391</v>
+        <v>1.793901884627268</v>
       </c>
       <c r="F990">
         <v>-1</v>
@@ -51500,10 +51500,10 @@
         <v>0.01583758948669285</v>
       </c>
       <c r="H990">
-        <v>0.01589460674405261</v>
+        <v>0.01554609811537273</v>
       </c>
       <c r="I990">
-        <v>0.137017257359755</v>
+        <v>0.3885086286798778</v>
       </c>
       <c r="J990">
         <v>1.212715716996954</v>
@@ -51515,10 +51515,10 @@
         <v>9.01</v>
       </c>
       <c r="M990">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N990">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O990">
         <v>1</v>
@@ -51541,7 +51541,7 @@
         <v>239</v>
       </c>
       <c r="E991">
-        <v>1.927173185661217</v>
+        <v>1.676509975954307</v>
       </c>
       <c r="F991">
         <v>-1</v>
@@ -51550,10 +51550,10 @@
         <v>0.0159541532337526</v>
       </c>
       <c r="H991">
-        <v>0.01601282681433878</v>
+        <v>0.01566349002404569</v>
       </c>
       <c r="I991">
-        <v>0.1386735805861816</v>
+        <v>0.3893367902930915</v>
       </c>
       <c r="J991">
         <v>1.233419757327283</v>
@@ -51565,10 +51565,10 @@
         <v>9.01</v>
       </c>
       <c r="M991">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N991">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O991">
         <v>1</v>
@@ -51591,7 +51591,7 @@
         <v>239</v>
       </c>
       <c r="E992">
-        <v>1.814249243380429</v>
+        <v>1.564377094565154</v>
       </c>
       <c r="F992">
         <v>-1</v>
@@ -51600,10 +51600,10 @@
         <v>0.01606549505425012</v>
       </c>
       <c r="H992">
-        <v>0.01612575075661957</v>
+        <v>0.01577562290543484</v>
       </c>
       <c r="I992">
-        <v>0.1402557023694504</v>
+        <v>0.390127851184725</v>
       </c>
       <c r="J992">
         <v>1.253196279618139</v>
@@ -51615,10 +51615,10 @@
         <v>9.01</v>
       </c>
       <c r="M992">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N992">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O992">
         <v>1</v>
@@ -51641,7 +51641,7 @@
         <v>239</v>
       </c>
       <c r="E993">
-        <v>1.727913647163381</v>
+        <v>1.478646301123707</v>
       </c>
       <c r="F993">
         <v>-1</v>
@@ -51650,10 +51650,10 @@
         <v>0.01615062104491597</v>
       </c>
       <c r="H993">
-        <v>0.01621208635283662</v>
+        <v>0.01586135369887629</v>
       </c>
       <c r="I993">
-        <v>0.1414653079206527</v>
+        <v>0.3907326539603266</v>
       </c>
       <c r="J993">
         <v>1.268316349008165</v>
@@ -51665,10 +51665,10 @@
         <v>9.01</v>
       </c>
       <c r="M993">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N993">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O993">
         <v>1</v>
@@ -51691,7 +51691,7 @@
         <v>239</v>
       </c>
       <c r="E994">
-        <v>1.718928010011864</v>
+        <v>1.469723610642253</v>
       </c>
       <c r="F994">
         <v>-1</v>
@@ -51700,10 +51700,10 @@
         <v>0.01615948078872736</v>
       </c>
       <c r="H994">
-        <v>0.01622107198998814</v>
+        <v>0.01587027638935775</v>
       </c>
       <c r="I994">
-        <v>0.1415912012607787</v>
+        <v>0.3907956006303897</v>
       </c>
       <c r="J994">
         <v>1.269890015759744</v>
@@ -51715,10 +51715,10 @@
         <v>9.01</v>
       </c>
       <c r="M994">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N994">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O994">
         <v>1</v>
@@ -51741,7 +51741,7 @@
         <v>239</v>
       </c>
       <c r="E995">
-        <v>1.728931826925575</v>
+        <v>1.47965734827811</v>
       </c>
       <c r="F995">
         <v>-1</v>
@@ -51750,10 +51750,10 @@
         <v>0.01614961713036935</v>
       </c>
       <c r="H995">
-        <v>0.01621106817307443</v>
+        <v>0.01586034265172189</v>
       </c>
       <c r="I995">
-        <v>0.1414510427050697</v>
+        <v>0.3907255213525351</v>
       </c>
       <c r="J995">
         <v>1.268138033813385</v>
@@ -51765,10 +51765,10 @@
         <v>9.01</v>
       </c>
       <c r="M995">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N995">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O995">
         <v>1</v>
@@ -51791,7 +51791,7 @@
         <v>239</v>
       </c>
       <c r="E996">
-        <v>1.716778388585936</v>
+        <v>1.467589047860288</v>
       </c>
       <c r="F996">
         <v>-1</v>
@@ -51800,10 +51800,10 @@
         <v>0.01616160029286536</v>
       </c>
       <c r="H996">
-        <v>0.01622322161141406</v>
+        <v>0.01587241095213971</v>
       </c>
       <c r="I996">
-        <v>0.1416213185487072</v>
+        <v>0.3908106592743543</v>
       </c>
       <c r="J996">
         <v>1.270266481858856</v>
@@ -51815,10 +51815,10 @@
         <v>9.01</v>
       </c>
       <c r="M996">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="N996">
-        <v>8.970000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="O996">
         <v>1</v>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3000" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2997" uniqueCount="551">
   <si>
     <t>trade_time</t>
   </si>
@@ -733,7 +733,7 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-11-10</t>
+    <t>2021-11-11</t>
   </si>
   <si>
     <t>2016-10-31</t>
@@ -1667,9 +1667,6 @@
   </si>
   <si>
     <t>2021-09-23</t>
-  </si>
-  <si>
-    <t>2021-09-24</t>
   </si>
 </sst>
 </file>
@@ -2027,7 +2024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P996"/>
+  <dimension ref="A1:P995"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51091,7 +51088,7 @@
         <v>239</v>
       </c>
       <c r="E982">
-        <v>2.281163145887622</v>
+        <v>2.408627566155303</v>
       </c>
       <c r="F982">
         <v>-1</v>
@@ -51100,10 +51097,10 @@
         <v>0.01535376569464774</v>
       </c>
       <c r="H982">
-        <v>0.01505883685411238</v>
+        <v>0.0152313724338447</v>
       </c>
       <c r="I982">
-        <v>0.385071159464637</v>
+        <v>0.2576067391969561</v>
       </c>
       <c r="J982">
         <v>1.12677898661594</v>
@@ -51115,10 +51112,10 @@
         <v>9.01</v>
       </c>
       <c r="M982">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N982">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O982">
         <v>1</v>
@@ -51141,7 +51138,7 @@
         <v>239</v>
       </c>
       <c r="E983">
-        <v>2.192933788190169</v>
+        <v>2.32008699379225</v>
       </c>
       <c r="F983">
         <v>-1</v>
@@ -51150,10 +51147,10 @@
         <v>0.01544137262301399</v>
       </c>
       <c r="H983">
-        <v>0.01514706621180983</v>
+        <v>0.01531991300620775</v>
       </c>
       <c r="I983">
-        <v>0.3856935887958359</v>
+        <v>0.2585403831937549</v>
       </c>
       <c r="J983">
         <v>1.142339719895914</v>
@@ -51165,10 +51162,10 @@
         <v>9.01</v>
       </c>
       <c r="M983">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N983">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O983">
         <v>1</v>
@@ -51191,7 +51188,7 @@
         <v>239</v>
       </c>
       <c r="E984">
-        <v>2.019841016572975</v>
+        <v>2.146383665661416</v>
       </c>
       <c r="F984">
         <v>-1</v>
@@ -51200,10 +51197,10 @@
         <v>0.01561324428160391</v>
       </c>
       <c r="H984">
-        <v>0.01532015898342702</v>
+        <v>0.01549361633433858</v>
       </c>
       <c r="I984">
-        <v>0.3869147018231187</v>
+        <v>0.2603720527346782</v>
       </c>
       <c r="J984">
         <v>1.172867545577958</v>
@@ -51215,10 +51212,10 @@
         <v>9.01</v>
       </c>
       <c r="M984">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N984">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O984">
         <v>1</v>
@@ -51241,7 +51238,7 @@
         <v>239</v>
       </c>
       <c r="E985">
-        <v>1.949866546240498</v>
+        <v>2.076162371800429</v>
       </c>
       <c r="F985">
         <v>-1</v>
@@ -51250,10 +51247,10 @@
         <v>0.01568272510487936</v>
       </c>
       <c r="H985">
-        <v>0.0153901334537595</v>
+        <v>0.01556383762819957</v>
       </c>
       <c r="I985">
-        <v>0.387408348880137</v>
+        <v>0.2611125233202065</v>
       </c>
       <c r="J985">
         <v>1.18520872200344</v>
@@ -51265,10 +51262,10 @@
         <v>9.01</v>
       </c>
       <c r="M985">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N985">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O985">
         <v>1</v>
@@ -51291,7 +51288,7 @@
         <v>239</v>
       </c>
       <c r="E986">
-        <v>1.932211967136382</v>
+        <v>2.05844551904868</v>
       </c>
       <c r="F986">
         <v>-1</v>
@@ -51300,10 +51297,10 @@
         <v>0.01570025513668821</v>
       </c>
       <c r="H986">
-        <v>0.01540778803286362</v>
+        <v>0.01558155448095132</v>
       </c>
       <c r="I986">
-        <v>0.3875328961754052</v>
+        <v>0.2612993442631071</v>
       </c>
       <c r="J986">
         <v>1.188322404385118</v>
@@ -51315,10 +51312,10 @@
         <v>9.01</v>
       </c>
       <c r="M986">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N986">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O986">
         <v>1</v>
@@ -51341,7 +51338,7 @@
         <v>239</v>
       </c>
       <c r="E987">
-        <v>1.923103548104354</v>
+        <v>2.049304971554457</v>
       </c>
       <c r="F987">
         <v>-1</v>
@@ -51350,10 +51347,10 @@
         <v>0.01570929929879585</v>
       </c>
       <c r="H987">
-        <v>0.01541689645189565</v>
+        <v>0.01559069502844554</v>
       </c>
       <c r="I987">
-        <v>0.3875971530997928</v>
+        <v>0.2613957296496903</v>
       </c>
       <c r="J987">
         <v>1.189928827494823</v>
@@ -51365,10 +51362,10 @@
         <v>9.01</v>
       </c>
       <c r="M987">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N987">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O987">
         <v>1</v>
@@ -51391,7 +51388,7 @@
         <v>239</v>
       </c>
       <c r="E988">
-        <v>1.89985779265028</v>
+        <v>2.025977220490316</v>
       </c>
       <c r="F988">
         <v>-1</v>
@@ -51400,10 +51397,10 @@
         <v>0.01573238106302979</v>
       </c>
       <c r="H988">
-        <v>0.01544014220734972</v>
+        <v>0.01561402277950969</v>
       </c>
       <c r="I988">
-        <v>0.3877611443199278</v>
+        <v>0.2616417164798914</v>
       </c>
       <c r="J988">
         <v>1.194028607998187</v>
@@ -51415,10 +51412,10 @@
         <v>9.01</v>
       </c>
       <c r="M988">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N988">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O988">
         <v>1</v>
@@ -51441,7 +51438,7 @@
         <v>239</v>
       </c>
       <c r="E989">
-        <v>1.870711999016381</v>
+        <v>1.996728619824198</v>
       </c>
       <c r="F989">
         <v>-1</v>
@@ -51450,10 +51447,10 @@
         <v>0.01576132124259925</v>
       </c>
       <c r="H989">
-        <v>0.01546928800098362</v>
+        <v>0.0156432713801758</v>
       </c>
       <c r="I989">
-        <v>0.3879667583843638</v>
+        <v>0.2619501375765463</v>
       </c>
       <c r="J989">
         <v>1.199168959609104</v>
@@ -51465,10 +51462,10 @@
         <v>9.01</v>
       </c>
       <c r="M989">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N989">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O989">
         <v>1</v>
@@ -51491,7 +51488,7 @@
         <v>239</v>
       </c>
       <c r="E990">
-        <v>1.793901884627268</v>
+        <v>1.919647570287329</v>
       </c>
       <c r="F990">
         <v>-1</v>
@@ -51500,10 +51497,10 @@
         <v>0.01583758948669285</v>
       </c>
       <c r="H990">
-        <v>0.01554609811537273</v>
+        <v>0.01572035242971267</v>
       </c>
       <c r="I990">
-        <v>0.3885086286798778</v>
+        <v>0.2627629430198173</v>
       </c>
       <c r="J990">
         <v>1.212715716996954</v>
@@ -51515,10 +51512,10 @@
         <v>9.01</v>
       </c>
       <c r="M990">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N990">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O990">
         <v>1</v>
@@ -51541,7 +51538,7 @@
         <v>239</v>
       </c>
       <c r="E991">
-        <v>1.676509975954307</v>
+        <v>1.801841580807761</v>
       </c>
       <c r="F991">
         <v>-1</v>
@@ -51550,10 +51547,10 @@
         <v>0.0159541532337526</v>
       </c>
       <c r="H991">
-        <v>0.01566349002404569</v>
+        <v>0.01583815841919224</v>
       </c>
       <c r="I991">
-        <v>0.3893367902930915</v>
+        <v>0.264005185439637</v>
       </c>
       <c r="J991">
         <v>1.233419757327283</v>
@@ -51565,10 +51562,10 @@
         <v>9.01</v>
       </c>
       <c r="M991">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N991">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O991">
         <v>1</v>
@@ -51591,7 +51588,7 @@
         <v>239</v>
       </c>
       <c r="E992">
-        <v>1.564377094565154</v>
+        <v>1.689313168972791</v>
       </c>
       <c r="F992">
         <v>-1</v>
@@ -51600,10 +51597,10 @@
         <v>0.01606549505425012</v>
       </c>
       <c r="H992">
-        <v>0.01577562290543484</v>
+        <v>0.01595068683102721</v>
       </c>
       <c r="I992">
-        <v>0.390127851184725</v>
+        <v>0.2651917767770886</v>
       </c>
       <c r="J992">
         <v>1.253196279618139</v>
@@ -51615,10 +51612,10 @@
         <v>9.01</v>
       </c>
       <c r="M992">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N992">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O992">
         <v>1</v>
@@ -51641,7 +51638,7 @@
         <v>239</v>
       </c>
       <c r="E993">
-        <v>1.478646301123707</v>
+        <v>1.603279974143543</v>
       </c>
       <c r="F993">
         <v>-1</v>
@@ -51650,10 +51647,10 @@
         <v>0.01615062104491597</v>
       </c>
       <c r="H993">
-        <v>0.01586135369887629</v>
+        <v>0.01603672002585646</v>
       </c>
       <c r="I993">
-        <v>0.3907326539603266</v>
+        <v>0.2660989809404901</v>
       </c>
       <c r="J993">
         <v>1.268316349008165</v>
@@ -51665,10 +51662,10 @@
         <v>9.01</v>
       </c>
       <c r="M993">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N993">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O993">
         <v>1</v>
@@ -51691,7 +51688,7 @@
         <v>239</v>
       </c>
       <c r="E994">
-        <v>1.469723610642253</v>
+        <v>1.594325810327058</v>
       </c>
       <c r="F994">
         <v>-1</v>
@@ -51700,10 +51697,10 @@
         <v>0.01615948078872736</v>
       </c>
       <c r="H994">
-        <v>0.01587027638935775</v>
+        <v>0.01604567418967294</v>
       </c>
       <c r="I994">
-        <v>0.3907956006303897</v>
+        <v>0.2661934009455846</v>
       </c>
       <c r="J994">
         <v>1.269890015759744</v>
@@ -51715,10 +51712,10 @@
         <v>9.01</v>
       </c>
       <c r="M994">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N994">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O994">
         <v>1</v>
@@ -51741,7 +51738,7 @@
         <v>239</v>
       </c>
       <c r="E995">
-        <v>1.47965734827811</v>
+        <v>1.604294587601842</v>
       </c>
       <c r="F995">
         <v>-1</v>
@@ -51750,10 +51747,10 @@
         <v>0.01614961713036935</v>
       </c>
       <c r="H995">
-        <v>0.01586034265172189</v>
+        <v>0.01603570541239816</v>
       </c>
       <c r="I995">
-        <v>0.3907255213525351</v>
+        <v>0.2660882820288029</v>
       </c>
       <c r="J995">
         <v>1.268138033813385</v>
@@ -51765,66 +51762,16 @@
         <v>9.01</v>
       </c>
       <c r="M995">
-        <v>5.67</v>
+        <v>5.69</v>
       </c>
       <c r="N995">
-        <v>8.67</v>
+        <v>8.82</v>
       </c>
       <c r="O995">
         <v>1</v>
       </c>
       <c r="P995" t="s">
         <v>550</v>
-      </c>
-    </row>
-    <row r="996" spans="1:16">
-      <c r="A996" s="1">
-        <v>0</v>
-      </c>
-      <c r="B996" t="s">
-        <v>100</v>
-      </c>
-      <c r="C996">
-        <v>1.858399707134643</v>
-      </c>
-      <c r="D996" t="s">
-        <v>239</v>
-      </c>
-      <c r="E996">
-        <v>1.467589047860288</v>
-      </c>
-      <c r="F996">
-        <v>-1</v>
-      </c>
-      <c r="G996">
-        <v>0.01616160029286536</v>
-      </c>
-      <c r="H996">
-        <v>0.01587241095213971</v>
-      </c>
-      <c r="I996">
-        <v>0.3908106592743543</v>
-      </c>
-      <c r="J996">
-        <v>1.270266481858856</v>
-      </c>
-      <c r="K996">
-        <v>5.63</v>
-      </c>
-      <c r="L996">
-        <v>9.01</v>
-      </c>
-      <c r="M996">
-        <v>5.67</v>
-      </c>
-      <c r="N996">
-        <v>8.67</v>
-      </c>
-      <c r="O996">
-        <v>1</v>
-      </c>
-      <c r="P996" t="s">
-        <v>551</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2976" uniqueCount="543">
   <si>
     <t>trade_time</t>
   </si>
@@ -736,7 +736,7 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-11-15</t>
+    <t>2021-11-16</t>
   </si>
   <si>
     <t>2016-10-31</t>
@@ -1643,12 +1643,6 @@
   </si>
   <si>
     <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
-    <t>2021-09-09</t>
   </si>
 </sst>
 </file>
@@ -2006,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P990"/>
+  <dimension ref="A1:P988"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51070,7 +51064,7 @@
         <v>240</v>
       </c>
       <c r="E982">
-        <v>2.388627566155304</v>
+        <v>2.347359776289143</v>
       </c>
       <c r="F982">
         <v>-1</v>
@@ -51079,10 +51073,10 @@
         <v>0.01535376569464774</v>
       </c>
       <c r="H982">
-        <v>0.0152113724338447</v>
+        <v>0.01519264022371086</v>
       </c>
       <c r="I982">
-        <v>0.2776067391969557</v>
+        <v>0.3188745290631161</v>
       </c>
       <c r="J982">
         <v>1.12677898661594</v>
@@ -51094,10 +51088,10 @@
         <v>9.01</v>
       </c>
       <c r="M982">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="N982">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="O982">
         <v>1</v>
@@ -51120,7 +51114,7 @@
         <v>240</v>
       </c>
       <c r="E983">
-        <v>2.388627566155304</v>
+        <v>2.347359776289143</v>
       </c>
       <c r="F983">
         <v>-1</v>
@@ -51129,10 +51123,10 @@
         <v>0.01558897917304165</v>
       </c>
       <c r="H983">
-        <v>0.0152113724338447</v>
+        <v>0.01519264022371086</v>
       </c>
       <c r="I983">
-        <v>0.242393260803043</v>
+        <v>0.2836610506692034</v>
       </c>
       <c r="J983">
         <v>1.12677898661594</v>
@@ -51144,10 +51138,10 @@
         <v>9.109999999999999</v>
       </c>
       <c r="M983">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="N983">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="O983">
         <v>1</v>
@@ -51170,7 +51164,7 @@
         <v>240</v>
       </c>
       <c r="E984">
-        <v>2.300086993792251</v>
+        <v>2.258663596593291</v>
       </c>
       <c r="F984">
         <v>-1</v>
@@ -51179,10 +51173,10 @@
         <v>0.01544137262301399</v>
       </c>
       <c r="H984">
-        <v>0.01529991300620775</v>
+        <v>0.01528133640340671</v>
       </c>
       <c r="I984">
-        <v>0.2785403831937545</v>
+        <v>0.3199637803927144</v>
       </c>
       <c r="J984">
         <v>1.142339719895914</v>
@@ -51194,10 +51188,10 @@
         <v>9.01</v>
       </c>
       <c r="M984">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="N984">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="O984">
         <v>1</v>
@@ -51220,7 +51214,7 @@
         <v>240</v>
       </c>
       <c r="E985">
-        <v>2.300086993792251</v>
+        <v>2.258663596593291</v>
       </c>
       <c r="F985">
         <v>-1</v>
@@ -51229,10 +51223,10 @@
         <v>0.01567845338940151</v>
       </c>
       <c r="H985">
-        <v>0.01529991300620775</v>
+        <v>0.01528133640340671</v>
       </c>
       <c r="I985">
-        <v>0.2414596168062451</v>
+        <v>0.282883014005205</v>
       </c>
       <c r="J985">
         <v>1.142339719895914</v>
@@ -51244,10 +51238,10 @@
         <v>9.109999999999999</v>
       </c>
       <c r="M985">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="N985">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="O985">
         <v>1</v>
@@ -51270,7 +51264,7 @@
         <v>240</v>
       </c>
       <c r="E986">
-        <v>2.126383665661416</v>
+        <v>2.084654990205636</v>
       </c>
       <c r="F986">
         <v>-1</v>
@@ -51279,10 +51273,10 @@
         <v>0.01561324428160391</v>
       </c>
       <c r="H986">
-        <v>0.01547361633433859</v>
+        <v>0.01545534500979436</v>
       </c>
       <c r="I986">
-        <v>0.2803720527346778</v>
+        <v>0.322100728190458</v>
       </c>
       <c r="J986">
         <v>1.172867545577958</v>
@@ -51294,10 +51288,10 @@
         <v>9.01</v>
       </c>
       <c r="M986">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="N986">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="O986">
         <v>1</v>
@@ -51320,7 +51314,7 @@
         <v>240</v>
       </c>
       <c r="E987">
-        <v>2.056162371800429</v>
+        <v>2.014310284580394</v>
       </c>
       <c r="F987">
         <v>-1</v>
@@ -51329,10 +51323,10 @@
         <v>0.01568272510487936</v>
       </c>
       <c r="H987">
-        <v>0.01554383762819957</v>
+        <v>0.01552568971541961</v>
       </c>
       <c r="I987">
-        <v>0.2811125233202061</v>
+        <v>0.3229646105402413</v>
       </c>
       <c r="J987">
         <v>1.18520872200344</v>
@@ -51344,10 +51338,10 @@
         <v>9.01</v>
       </c>
       <c r="M987">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="N987">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="O987">
         <v>1</v>
@@ -51370,7 +51364,7 @@
         <v>240</v>
       </c>
       <c r="E988">
-        <v>2.038445519048681</v>
+        <v>1.996562295004829</v>
       </c>
       <c r="F988">
         <v>-1</v>
@@ -51379,10 +51373,10 @@
         <v>0.01570025513668821</v>
       </c>
       <c r="H988">
-        <v>0.01556155448095132</v>
+        <v>0.01554343770499517</v>
       </c>
       <c r="I988">
-        <v>0.2812993442631067</v>
+        <v>0.3231825683069589</v>
       </c>
       <c r="J988">
         <v>1.188322404385118</v>
@@ -51394,116 +51388,16 @@
         <v>9.01</v>
       </c>
       <c r="M988">
-        <v>5.69</v>
+        <v>5.7</v>
       </c>
       <c r="N988">
-        <v>8.800000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="O988">
         <v>1</v>
       </c>
       <c r="P988" t="s">
         <v>542</v>
-      </c>
-    </row>
-    <row r="989" spans="1:16">
-      <c r="A989" s="1">
-        <v>0</v>
-      </c>
-      <c r="B989" t="s">
-        <v>100</v>
-      </c>
-      <c r="C989">
-        <v>2.310700701204147</v>
-      </c>
-      <c r="D989" t="s">
-        <v>240</v>
-      </c>
-      <c r="E989">
-        <v>2.029304971554457</v>
-      </c>
-      <c r="F989">
-        <v>-1</v>
-      </c>
-      <c r="G989">
-        <v>0.01570929929879585</v>
-      </c>
-      <c r="H989">
-        <v>0.01557069502844555</v>
-      </c>
-      <c r="I989">
-        <v>0.2813957296496898</v>
-      </c>
-      <c r="J989">
-        <v>1.189928827494823</v>
-      </c>
-      <c r="K989">
-        <v>5.63</v>
-      </c>
-      <c r="L989">
-        <v>9.01</v>
-      </c>
-      <c r="M989">
-        <v>5.69</v>
-      </c>
-      <c r="N989">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O989">
-        <v>1</v>
-      </c>
-      <c r="P989" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="990" spans="1:16">
-      <c r="A990" s="1">
-        <v>0</v>
-      </c>
-      <c r="B990" t="s">
-        <v>100</v>
-      </c>
-      <c r="C990">
-        <v>2.287618936970207</v>
-      </c>
-      <c r="D990" t="s">
-        <v>240</v>
-      </c>
-      <c r="E990">
-        <v>2.005977220490316</v>
-      </c>
-      <c r="F990">
-        <v>-1</v>
-      </c>
-      <c r="G990">
-        <v>0.01573238106302979</v>
-      </c>
-      <c r="H990">
-        <v>0.01559402277950969</v>
-      </c>
-      <c r="I990">
-        <v>0.281641716479891</v>
-      </c>
-      <c r="J990">
-        <v>1.194028607998187</v>
-      </c>
-      <c r="K990">
-        <v>5.63</v>
-      </c>
-      <c r="L990">
-        <v>9.01</v>
-      </c>
-      <c r="M990">
-        <v>5.69</v>
-      </c>
-      <c r="N990">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O990">
-        <v>1</v>
-      </c>
-      <c r="P990" t="s">
-        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -736,7 +736,7 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-11-16</t>
+    <t>2021-11-17</t>
   </si>
   <si>
     <t>2016-10-31</t>
@@ -51064,7 +51064,7 @@
         <v>240</v>
       </c>
       <c r="E982">
-        <v>2.347359776289143</v>
+        <v>2.199895356021463</v>
       </c>
       <c r="F982">
         <v>-1</v>
@@ -51073,10 +51073,10 @@
         <v>0.01535376569464774</v>
       </c>
       <c r="H982">
-        <v>0.01519264022371086</v>
+        <v>0.01500010464397854</v>
       </c>
       <c r="I982">
-        <v>0.3188745290631161</v>
+        <v>0.4663389493307966</v>
       </c>
       <c r="J982">
         <v>1.12677898661594</v>
@@ -51088,10 +51088,10 @@
         <v>9.01</v>
       </c>
       <c r="M982">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="N982">
-        <v>8.77</v>
+        <v>8.6</v>
       </c>
       <c r="O982">
         <v>1</v>
@@ -51114,7 +51114,7 @@
         <v>240</v>
       </c>
       <c r="E983">
-        <v>2.347359776289143</v>
+        <v>2.199895356021463</v>
       </c>
       <c r="F983">
         <v>-1</v>
@@ -51123,10 +51123,10 @@
         <v>0.01558897917304165</v>
       </c>
       <c r="H983">
-        <v>0.01519264022371086</v>
+        <v>0.01500010464397854</v>
       </c>
       <c r="I983">
-        <v>0.2836610506692034</v>
+        <v>0.4311254709368839</v>
       </c>
       <c r="J983">
         <v>1.12677898661594</v>
@@ -51138,10 +51138,10 @@
         <v>9.109999999999999</v>
       </c>
       <c r="M983">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="N983">
-        <v>8.77</v>
+        <v>8.6</v>
       </c>
       <c r="O983">
         <v>1</v>
@@ -51164,7 +51164,7 @@
         <v>240</v>
       </c>
       <c r="E984">
-        <v>2.258663596593291</v>
+        <v>2.11151039099121</v>
       </c>
       <c r="F984">
         <v>-1</v>
@@ -51173,10 +51173,10 @@
         <v>0.01544137262301399</v>
       </c>
       <c r="H984">
-        <v>0.01528133640340671</v>
+        <v>0.01508848960900879</v>
       </c>
       <c r="I984">
-        <v>0.3199637803927144</v>
+        <v>0.467116985994795</v>
       </c>
       <c r="J984">
         <v>1.142339719895914</v>
@@ -51188,10 +51188,10 @@
         <v>9.01</v>
       </c>
       <c r="M984">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="N984">
-        <v>8.77</v>
+        <v>8.6</v>
       </c>
       <c r="O984">
         <v>1</v>
@@ -51214,7 +51214,7 @@
         <v>240</v>
       </c>
       <c r="E985">
-        <v>2.258663596593291</v>
+        <v>2.11151039099121</v>
       </c>
       <c r="F985">
         <v>-1</v>
@@ -51223,10 +51223,10 @@
         <v>0.01567845338940151</v>
       </c>
       <c r="H985">
-        <v>0.01528133640340671</v>
+        <v>0.01508848960900879</v>
       </c>
       <c r="I985">
-        <v>0.282883014005205</v>
+        <v>0.4300362196072856</v>
       </c>
       <c r="J985">
         <v>1.142339719895914</v>
@@ -51238,10 +51238,10 @@
         <v>9.109999999999999</v>
       </c>
       <c r="M985">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="N985">
-        <v>8.77</v>
+        <v>8.6</v>
       </c>
       <c r="O985">
         <v>1</v>
@@ -51264,7 +51264,7 @@
         <v>240</v>
       </c>
       <c r="E986">
-        <v>2.084654990205636</v>
+        <v>1.938112341117196</v>
       </c>
       <c r="F986">
         <v>-1</v>
@@ -51273,10 +51273,10 @@
         <v>0.01561324428160391</v>
       </c>
       <c r="H986">
-        <v>0.01545534500979436</v>
+        <v>0.0152618876588828</v>
       </c>
       <c r="I986">
-        <v>0.322100728190458</v>
+        <v>0.468643377278898</v>
       </c>
       <c r="J986">
         <v>1.172867545577958</v>
@@ -51288,10 +51288,10 @@
         <v>9.01</v>
       </c>
       <c r="M986">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="N986">
-        <v>8.77</v>
+        <v>8.6</v>
       </c>
       <c r="O986">
         <v>1</v>
@@ -51314,7 +51314,7 @@
         <v>240</v>
       </c>
       <c r="E987">
-        <v>2.014310284580394</v>
+        <v>1.868014459020464</v>
       </c>
       <c r="F987">
         <v>-1</v>
@@ -51323,10 +51323,10 @@
         <v>0.01568272510487936</v>
       </c>
       <c r="H987">
-        <v>0.01552568971541961</v>
+        <v>0.01533198554097953</v>
       </c>
       <c r="I987">
-        <v>0.3229646105402413</v>
+        <v>0.4692604361001713</v>
       </c>
       <c r="J987">
         <v>1.18520872200344</v>
@@ -51338,10 +51338,10 @@
         <v>9.01</v>
       </c>
       <c r="M987">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="N987">
-        <v>8.77</v>
+        <v>8.6</v>
       </c>
       <c r="O987">
         <v>1</v>
@@ -51364,7 +51364,7 @@
         <v>240</v>
       </c>
       <c r="E988">
-        <v>1.996562295004829</v>
+        <v>1.850328743092532</v>
       </c>
       <c r="F988">
         <v>-1</v>
@@ -51373,10 +51373,10 @@
         <v>0.01570025513668821</v>
       </c>
       <c r="H988">
-        <v>0.01554343770499517</v>
+        <v>0.01534967125690747</v>
       </c>
       <c r="I988">
-        <v>0.3231825683069589</v>
+        <v>0.4694161202192557</v>
       </c>
       <c r="J988">
         <v>1.188322404385118</v>
@@ -51388,10 +51388,10 @@
         <v>9.01</v>
       </c>
       <c r="M988">
-        <v>5.7</v>
+        <v>5.68</v>
       </c>
       <c r="N988">
-        <v>8.77</v>
+        <v>8.6</v>
       </c>
       <c r="O988">
         <v>1</v>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -733,7 +733,7 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-11-23</t>
+    <t>2021-11-24</t>
   </si>
   <si>
     <t>2016-10-31</t>
@@ -51052,7 +51052,7 @@
         <v>239</v>
       </c>
       <c r="E982">
-        <v>2.281447783746173</v>
+        <v>2.146376624281535</v>
       </c>
       <c r="F982">
         <v>-1</v>
@@ -51061,10 +51061,10 @@
         <v>0.01535376569464774</v>
       </c>
       <c r="H982">
-        <v>0.01469855221625383</v>
+        <v>0.01465362337571847</v>
       </c>
       <c r="I982">
-        <v>0.3847865216060864</v>
+        <v>0.5198576810707243</v>
       </c>
       <c r="J982">
         <v>1.12677898661594</v>
@@ -51076,10 +51076,10 @@
         <v>9.01</v>
       </c>
       <c r="M982">
-        <v>5.51</v>
+        <v>5.55</v>
       </c>
       <c r="N982">
-        <v>8.49</v>
+        <v>8.4</v>
       </c>
       <c r="O982">
         <v>1</v>
@@ -51102,7 +51102,7 @@
         <v>239</v>
       </c>
       <c r="E983">
-        <v>2.195708143373515</v>
+        <v>2.06001455457768</v>
       </c>
       <c r="F983">
         <v>-1</v>
@@ -51111,10 +51111,10 @@
         <v>0.01544137262301399</v>
       </c>
       <c r="H983">
-        <v>0.01478429185662648</v>
+        <v>0.01473998544542232</v>
       </c>
       <c r="I983">
-        <v>0.3829192336124896</v>
+        <v>0.5186128224083255</v>
       </c>
       <c r="J983">
         <v>1.142339719895914</v>
@@ -51126,10 +51126,10 @@
         <v>9.01</v>
       </c>
       <c r="M983">
-        <v>5.51</v>
+        <v>5.55</v>
       </c>
       <c r="N983">
-        <v>8.49</v>
+        <v>8.4</v>
       </c>
       <c r="O983">
         <v>1</v>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="541">
   <si>
     <t>trade_time</t>
   </si>
@@ -733,7 +733,7 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-11-24</t>
+    <t>2021-11-25</t>
   </si>
   <si>
     <t>2016-10-31</t>
@@ -1631,6 +1631,12 @@
   </si>
   <si>
     <t>2021-08-25</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
   </si>
 </sst>
 </file>
@@ -1988,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P983"/>
+  <dimension ref="A1:P985"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51052,7 +51058,7 @@
         <v>239</v>
       </c>
       <c r="E982">
-        <v>2.146376624281535</v>
+        <v>2.090179993880014</v>
       </c>
       <c r="F982">
         <v>-1</v>
@@ -51061,10 +51067,10 @@
         <v>0.01535376569464774</v>
       </c>
       <c r="H982">
-        <v>0.01465362337571847</v>
+        <v>0.01452982000611999</v>
       </c>
       <c r="I982">
-        <v>0.5198576810707243</v>
+        <v>0.5760543114722454</v>
       </c>
       <c r="J982">
         <v>1.12677898661594</v>
@@ -51076,10 +51082,10 @@
         <v>9.01</v>
       </c>
       <c r="M982">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
       <c r="N982">
-        <v>8.4</v>
+        <v>8.31</v>
       </c>
       <c r="O982">
         <v>1</v>
@@ -51102,7 +51108,7 @@
         <v>239</v>
       </c>
       <c r="E983">
-        <v>2.06001455457768</v>
+        <v>2.004284746174557</v>
       </c>
       <c r="F983">
         <v>-1</v>
@@ -51111,10 +51117,10 @@
         <v>0.01544137262301399</v>
       </c>
       <c r="H983">
-        <v>0.01473998544542232</v>
+        <v>0.01461571525382544</v>
       </c>
       <c r="I983">
-        <v>0.5186128224083255</v>
+        <v>0.5743426308114481</v>
       </c>
       <c r="J983">
         <v>1.142339719895914</v>
@@ -51126,16 +51132,116 @@
         <v>9.01</v>
       </c>
       <c r="M983">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
       <c r="N983">
-        <v>8.4</v>
+        <v>8.31</v>
       </c>
       <c r="O983">
         <v>1</v>
       </c>
       <c r="P983" t="s">
         <v>538</v>
+      </c>
+    </row>
+    <row r="984" spans="1:16">
+      <c r="A984" s="1">
+        <v>0</v>
+      </c>
+      <c r="B984" t="s">
+        <v>100</v>
+      </c>
+      <c r="C984">
+        <v>2.406755718396094</v>
+      </c>
+      <c r="D984" t="s">
+        <v>239</v>
+      </c>
+      <c r="E984">
+        <v>1.835771148409671</v>
+      </c>
+      <c r="F984">
+        <v>-1</v>
+      </c>
+      <c r="G984">
+        <v>0.01561324428160391</v>
+      </c>
+      <c r="H984">
+        <v>0.01478422885159033</v>
+      </c>
+      <c r="I984">
+        <v>0.5709845699864236</v>
+      </c>
+      <c r="J984">
+        <v>1.172867545577958</v>
+      </c>
+      <c r="K984">
+        <v>5.63</v>
+      </c>
+      <c r="L984">
+        <v>9.01</v>
+      </c>
+      <c r="M984">
+        <v>5.52</v>
+      </c>
+      <c r="N984">
+        <v>8.31</v>
+      </c>
+      <c r="O984">
+        <v>1</v>
+      </c>
+      <c r="P984" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="985" spans="1:16">
+      <c r="A985" s="1">
+        <v>0</v>
+      </c>
+      <c r="B985" t="s">
+        <v>100</v>
+      </c>
+      <c r="C985">
+        <v>2.337274895120635</v>
+      </c>
+      <c r="D985" t="s">
+        <v>239</v>
+      </c>
+      <c r="E985">
+        <v>1.767647854541015</v>
+      </c>
+      <c r="F985">
+        <v>-1</v>
+      </c>
+      <c r="G985">
+        <v>0.01568272510487936</v>
+      </c>
+      <c r="H985">
+        <v>0.01485235214545899</v>
+      </c>
+      <c r="I985">
+        <v>0.5696270405796202</v>
+      </c>
+      <c r="J985">
+        <v>1.18520872200344</v>
+      </c>
+      <c r="K985">
+        <v>5.63</v>
+      </c>
+      <c r="L985">
+        <v>9.01</v>
+      </c>
+      <c r="M985">
+        <v>5.52</v>
+      </c>
+      <c r="N985">
+        <v>8.31</v>
+      </c>
+      <c r="O985">
+        <v>1</v>
+      </c>
+      <c r="P985" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="538">
   <si>
     <t>trade_time</t>
   </si>
@@ -316,7 +316,7 @@
     <t>2021-03-22</t>
   </si>
   <si>
-    <t>2021-11-08</t>
+    <t>2021-09-29</t>
   </si>
   <si>
     <t>2016-12-12</t>
@@ -733,7 +733,7 @@
     <t>2021-04-07</t>
   </si>
   <si>
-    <t>2021-11-25</t>
+    <t>2021-10-29</t>
   </si>
   <si>
     <t>2016-10-31</t>
@@ -1627,16 +1627,7 @@
     <t>2020-11-05</t>
   </si>
   <si>
-    <t>2021-08-24</t>
-  </si>
-  <si>
-    <t>2021-08-25</t>
-  </si>
-  <si>
-    <t>2021-09-01</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
+    <t>2021-09-27</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +1985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P985"/>
+  <dimension ref="A1:P982"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51052,196 +51043,46 @@
         <v>100</v>
       </c>
       <c r="C982">
-        <v>2.666234305352259</v>
+        <v>0.7626869004855017</v>
       </c>
       <c r="D982" t="s">
         <v>239</v>
       </c>
       <c r="E982">
-        <v>2.090179993880014</v>
+        <v>1.551008039856243</v>
       </c>
       <c r="F982">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G982">
-        <v>0.01535376569464774</v>
+        <v>0.0137173130995145</v>
       </c>
       <c r="H982">
-        <v>0.01452982000611999</v>
+        <v>0.01546899196014376</v>
       </c>
       <c r="I982">
-        <v>0.5760543114722454</v>
+        <v>0.7883211393707414</v>
       </c>
       <c r="J982">
-        <v>1.12677898661594</v>
+        <v>1.267575949024364</v>
       </c>
       <c r="K982">
-        <v>5.63</v>
+        <v>5.11</v>
       </c>
       <c r="L982">
-        <v>9.01</v>
+        <v>7.24</v>
       </c>
       <c r="M982">
-        <v>5.52</v>
+        <v>5.49</v>
       </c>
       <c r="N982">
-        <v>8.31</v>
+        <v>8.51</v>
       </c>
       <c r="O982">
         <v>1</v>
       </c>
       <c r="P982" t="s">
         <v>537</v>
-      </c>
-    </row>
-    <row r="983" spans="1:16">
-      <c r="A983" s="1">
-        <v>0</v>
-      </c>
-      <c r="B983" t="s">
-        <v>100</v>
-      </c>
-      <c r="C983">
-        <v>2.578627376986005</v>
-      </c>
-      <c r="D983" t="s">
-        <v>239</v>
-      </c>
-      <c r="E983">
-        <v>2.004284746174557</v>
-      </c>
-      <c r="F983">
-        <v>-1</v>
-      </c>
-      <c r="G983">
-        <v>0.01544137262301399</v>
-      </c>
-      <c r="H983">
-        <v>0.01461571525382544</v>
-      </c>
-      <c r="I983">
-        <v>0.5743426308114481</v>
-      </c>
-      <c r="J983">
-        <v>1.142339719895914</v>
-      </c>
-      <c r="K983">
-        <v>5.63</v>
-      </c>
-      <c r="L983">
-        <v>9.01</v>
-      </c>
-      <c r="M983">
-        <v>5.52</v>
-      </c>
-      <c r="N983">
-        <v>8.31</v>
-      </c>
-      <c r="O983">
-        <v>1</v>
-      </c>
-      <c r="P983" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="984" spans="1:16">
-      <c r="A984" s="1">
-        <v>0</v>
-      </c>
-      <c r="B984" t="s">
-        <v>100</v>
-      </c>
-      <c r="C984">
-        <v>2.406755718396094</v>
-      </c>
-      <c r="D984" t="s">
-        <v>239</v>
-      </c>
-      <c r="E984">
-        <v>1.835771148409671</v>
-      </c>
-      <c r="F984">
-        <v>-1</v>
-      </c>
-      <c r="G984">
-        <v>0.01561324428160391</v>
-      </c>
-      <c r="H984">
-        <v>0.01478422885159033</v>
-      </c>
-      <c r="I984">
-        <v>0.5709845699864236</v>
-      </c>
-      <c r="J984">
-        <v>1.172867545577958</v>
-      </c>
-      <c r="K984">
-        <v>5.63</v>
-      </c>
-      <c r="L984">
-        <v>9.01</v>
-      </c>
-      <c r="M984">
-        <v>5.52</v>
-      </c>
-      <c r="N984">
-        <v>8.31</v>
-      </c>
-      <c r="O984">
-        <v>1</v>
-      </c>
-      <c r="P984" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="985" spans="1:16">
-      <c r="A985" s="1">
-        <v>0</v>
-      </c>
-      <c r="B985" t="s">
-        <v>100</v>
-      </c>
-      <c r="C985">
-        <v>2.337274895120635</v>
-      </c>
-      <c r="D985" t="s">
-        <v>239</v>
-      </c>
-      <c r="E985">
-        <v>1.767647854541015</v>
-      </c>
-      <c r="F985">
-        <v>-1</v>
-      </c>
-      <c r="G985">
-        <v>0.01568272510487936</v>
-      </c>
-      <c r="H985">
-        <v>0.01485235214545899</v>
-      </c>
-      <c r="I985">
-        <v>0.5696270405796202</v>
-      </c>
-      <c r="J985">
-        <v>1.18520872200344</v>
-      </c>
-      <c r="K985">
-        <v>5.63</v>
-      </c>
-      <c r="L985">
-        <v>9.01</v>
-      </c>
-      <c r="M985">
-        <v>5.52</v>
-      </c>
-      <c r="N985">
-        <v>8.31</v>
-      </c>
-      <c r="O985">
-        <v>1</v>
-      </c>
-      <c r="P985" t="s">
-        <v>540</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2958" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="539">
   <si>
     <t>trade_time</t>
   </si>
@@ -1625,6 +1625,9 @@
   </si>
   <si>
     <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>2021-09-24</t>
   </si>
   <si>
     <t>2021-09-27</t>
@@ -1985,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P982"/>
+  <dimension ref="A1:P983"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51043,28 +51046,28 @@
         <v>100</v>
       </c>
       <c r="C982">
-        <v>0.7626869004855017</v>
+        <v>0.7489382777012477</v>
       </c>
       <c r="D982" t="s">
         <v>239</v>
       </c>
       <c r="E982">
-        <v>1.551008039856243</v>
+        <v>1.536237014594882</v>
       </c>
       <c r="F982">
         <v>1</v>
       </c>
       <c r="G982">
-        <v>0.0137173130995145</v>
+        <v>0.01373106172229875</v>
       </c>
       <c r="H982">
-        <v>0.01546899196014376</v>
+        <v>0.01548376298540512</v>
       </c>
       <c r="I982">
-        <v>0.7883211393707414</v>
+        <v>0.7872987368936348</v>
       </c>
       <c r="J982">
-        <v>1.267575949024364</v>
+        <v>1.270266481858856</v>
       </c>
       <c r="K982">
         <v>5.11</v>
@@ -51083,6 +51086,56 @@
       </c>
       <c r="P982" t="s">
         <v>537</v>
+      </c>
+    </row>
+    <row r="983" spans="1:16">
+      <c r="A983" s="1">
+        <v>0</v>
+      </c>
+      <c r="B983" t="s">
+        <v>100</v>
+      </c>
+      <c r="C983">
+        <v>0.7626869004855017</v>
+      </c>
+      <c r="D983" t="s">
+        <v>239</v>
+      </c>
+      <c r="E983">
+        <v>1.551008039856243</v>
+      </c>
+      <c r="F983">
+        <v>1</v>
+      </c>
+      <c r="G983">
+        <v>0.0137173130995145</v>
+      </c>
+      <c r="H983">
+        <v>0.01546899196014376</v>
+      </c>
+      <c r="I983">
+        <v>0.7883211393707414</v>
+      </c>
+      <c r="J983">
+        <v>1.267575949024364</v>
+      </c>
+      <c r="K983">
+        <v>5.11</v>
+      </c>
+      <c r="L983">
+        <v>7.24</v>
+      </c>
+      <c r="M983">
+        <v>5.49</v>
+      </c>
+      <c r="N983">
+        <v>8.51</v>
+      </c>
+      <c r="O983">
+        <v>1</v>
+      </c>
+      <c r="P983" t="s">
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="541">
   <si>
     <t>trade_time</t>
   </si>
@@ -1625,6 +1625,12 @@
   </si>
   <si>
     <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
   </si>
   <si>
     <t>2021-09-24</t>
@@ -1988,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P983"/>
+  <dimension ref="A1:P985"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51046,28 +51052,28 @@
         <v>100</v>
       </c>
       <c r="C982">
-        <v>0.7489382777012477</v>
+        <v>0.7508620194677098</v>
       </c>
       <c r="D982" t="s">
         <v>239</v>
       </c>
       <c r="E982">
-        <v>1.536237014594882</v>
+        <v>1.538303813479007</v>
       </c>
       <c r="F982">
         <v>1</v>
       </c>
       <c r="G982">
-        <v>0.01373106172229875</v>
+        <v>0.01372913798053229</v>
       </c>
       <c r="H982">
-        <v>0.01548376298540512</v>
+        <v>0.01548169618652099</v>
       </c>
       <c r="I982">
-        <v>0.7872987368936348</v>
+        <v>0.787441794011297</v>
       </c>
       <c r="J982">
-        <v>1.270266481858856</v>
+        <v>1.269890015759744</v>
       </c>
       <c r="K982">
         <v>5.11</v>
@@ -51096,28 +51102,28 @@
         <v>100</v>
       </c>
       <c r="C983">
-        <v>0.7626869004855017</v>
+        <v>0.7598146472136049</v>
       </c>
       <c r="D983" t="s">
         <v>239</v>
       </c>
       <c r="E983">
-        <v>1.551008039856243</v>
+        <v>1.547922194364518</v>
       </c>
       <c r="F983">
         <v>1</v>
       </c>
       <c r="G983">
-        <v>0.0137173130995145</v>
+        <v>0.01372018535278639</v>
       </c>
       <c r="H983">
-        <v>0.01546899196014376</v>
+        <v>0.01547207780563548</v>
       </c>
       <c r="I983">
-        <v>0.7883211393707414</v>
+        <v>0.7881075471509131</v>
       </c>
       <c r="J983">
-        <v>1.267575949024364</v>
+        <v>1.268138033813385</v>
       </c>
       <c r="K983">
         <v>5.11</v>
@@ -51136,6 +51142,106 @@
       </c>
       <c r="P983" t="s">
         <v>538</v>
+      </c>
+    </row>
+    <row r="984" spans="1:16">
+      <c r="A984" s="1">
+        <v>0</v>
+      </c>
+      <c r="B984" t="s">
+        <v>100</v>
+      </c>
+      <c r="C984">
+        <v>0.7489382777012477</v>
+      </c>
+      <c r="D984" t="s">
+        <v>239</v>
+      </c>
+      <c r="E984">
+        <v>1.536237014594882</v>
+      </c>
+      <c r="F984">
+        <v>1</v>
+      </c>
+      <c r="G984">
+        <v>0.01373106172229875</v>
+      </c>
+      <c r="H984">
+        <v>0.01548376298540512</v>
+      </c>
+      <c r="I984">
+        <v>0.7872987368936348</v>
+      </c>
+      <c r="J984">
+        <v>1.270266481858856</v>
+      </c>
+      <c r="K984">
+        <v>5.11</v>
+      </c>
+      <c r="L984">
+        <v>7.24</v>
+      </c>
+      <c r="M984">
+        <v>5.49</v>
+      </c>
+      <c r="N984">
+        <v>8.51</v>
+      </c>
+      <c r="O984">
+        <v>1</v>
+      </c>
+      <c r="P984" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="985" spans="1:16">
+      <c r="A985" s="1">
+        <v>0</v>
+      </c>
+      <c r="B985" t="s">
+        <v>100</v>
+      </c>
+      <c r="C985">
+        <v>0.7626869004855017</v>
+      </c>
+      <c r="D985" t="s">
+        <v>239</v>
+      </c>
+      <c r="E985">
+        <v>1.551008039856243</v>
+      </c>
+      <c r="F985">
+        <v>1</v>
+      </c>
+      <c r="G985">
+        <v>0.0137173130995145</v>
+      </c>
+      <c r="H985">
+        <v>0.01546899196014376</v>
+      </c>
+      <c r="I985">
+        <v>0.7883211393707414</v>
+      </c>
+      <c r="J985">
+        <v>1.267575949024364</v>
+      </c>
+      <c r="K985">
+        <v>5.11</v>
+      </c>
+      <c r="L985">
+        <v>7.24</v>
+      </c>
+      <c r="M985">
+        <v>5.49</v>
+      </c>
+      <c r="N985">
+        <v>8.51</v>
+      </c>
+      <c r="O985">
+        <v>1</v>
+      </c>
+      <c r="P985" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2967" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="542">
   <si>
     <t>trade_time</t>
   </si>
@@ -1625,6 +1625,9 @@
   </si>
   <si>
     <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>2021-09-16</t>
   </si>
   <si>
     <t>2021-09-17</t>
@@ -1994,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P985"/>
+  <dimension ref="A1:P986"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51052,28 +51055,28 @@
         <v>100</v>
       </c>
       <c r="C982">
-        <v>0.7508620194677098</v>
+        <v>0.7589034565682784</v>
       </c>
       <c r="D982" t="s">
         <v>239</v>
       </c>
       <c r="E982">
-        <v>1.538303813479007</v>
+        <v>1.546943243945176</v>
       </c>
       <c r="F982">
         <v>1</v>
       </c>
       <c r="G982">
-        <v>0.01372913798053229</v>
+        <v>0.01372109654343172</v>
       </c>
       <c r="H982">
-        <v>0.01548169618652099</v>
+        <v>0.01547305675605482</v>
       </c>
       <c r="I982">
-        <v>0.787441794011297</v>
+        <v>0.7880397873768974</v>
       </c>
       <c r="J982">
-        <v>1.269890015759744</v>
+        <v>1.268316349008165</v>
       </c>
       <c r="K982">
         <v>5.11</v>
@@ -51102,28 +51105,28 @@
         <v>100</v>
       </c>
       <c r="C983">
-        <v>0.7598146472136049</v>
+        <v>0.7508620194677098</v>
       </c>
       <c r="D983" t="s">
         <v>239</v>
       </c>
       <c r="E983">
-        <v>1.547922194364518</v>
+        <v>1.538303813479007</v>
       </c>
       <c r="F983">
         <v>1</v>
       </c>
       <c r="G983">
-        <v>0.01372018535278639</v>
+        <v>0.01372913798053229</v>
       </c>
       <c r="H983">
-        <v>0.01547207780563548</v>
+        <v>0.01548169618652099</v>
       </c>
       <c r="I983">
-        <v>0.7881075471509131</v>
+        <v>0.787441794011297</v>
       </c>
       <c r="J983">
-        <v>1.268138033813385</v>
+        <v>1.269890015759744</v>
       </c>
       <c r="K983">
         <v>5.11</v>
@@ -51152,28 +51155,28 @@
         <v>100</v>
       </c>
       <c r="C984">
-        <v>0.7489382777012477</v>
+        <v>0.7598146472136049</v>
       </c>
       <c r="D984" t="s">
         <v>239</v>
       </c>
       <c r="E984">
-        <v>1.536237014594882</v>
+        <v>1.547922194364518</v>
       </c>
       <c r="F984">
         <v>1</v>
       </c>
       <c r="G984">
-        <v>0.01373106172229875</v>
+        <v>0.01372018535278639</v>
       </c>
       <c r="H984">
-        <v>0.01548376298540512</v>
+        <v>0.01547207780563548</v>
       </c>
       <c r="I984">
-        <v>0.7872987368936348</v>
+        <v>0.7881075471509131</v>
       </c>
       <c r="J984">
-        <v>1.270266481858856</v>
+        <v>1.268138033813385</v>
       </c>
       <c r="K984">
         <v>5.11</v>
@@ -51202,28 +51205,28 @@
         <v>100</v>
       </c>
       <c r="C985">
-        <v>0.7626869004855017</v>
+        <v>0.7489382777012477</v>
       </c>
       <c r="D985" t="s">
         <v>239</v>
       </c>
       <c r="E985">
-        <v>1.551008039856243</v>
+        <v>1.536237014594882</v>
       </c>
       <c r="F985">
         <v>1</v>
       </c>
       <c r="G985">
-        <v>0.0137173130995145</v>
+        <v>0.01373106172229875</v>
       </c>
       <c r="H985">
-        <v>0.01546899196014376</v>
+        <v>0.01548376298540512</v>
       </c>
       <c r="I985">
-        <v>0.7883211393707414</v>
+        <v>0.7872987368936348</v>
       </c>
       <c r="J985">
-        <v>1.267575949024364</v>
+        <v>1.270266481858856</v>
       </c>
       <c r="K985">
         <v>5.11</v>
@@ -51242,6 +51245,56 @@
       </c>
       <c r="P985" t="s">
         <v>540</v>
+      </c>
+    </row>
+    <row r="986" spans="1:16">
+      <c r="A986" s="1">
+        <v>0</v>
+      </c>
+      <c r="B986" t="s">
+        <v>100</v>
+      </c>
+      <c r="C986">
+        <v>0.7626869004855017</v>
+      </c>
+      <c r="D986" t="s">
+        <v>239</v>
+      </c>
+      <c r="E986">
+        <v>1.551008039856243</v>
+      </c>
+      <c r="F986">
+        <v>1</v>
+      </c>
+      <c r="G986">
+        <v>0.0137173130995145</v>
+      </c>
+      <c r="H986">
+        <v>0.01546899196014376</v>
+      </c>
+      <c r="I986">
+        <v>0.7883211393707414</v>
+      </c>
+      <c r="J986">
+        <v>1.267575949024364</v>
+      </c>
+      <c r="K986">
+        <v>5.11</v>
+      </c>
+      <c r="L986">
+        <v>7.24</v>
+      </c>
+      <c r="M986">
+        <v>5.49</v>
+      </c>
+      <c r="N986">
+        <v>8.51</v>
+      </c>
+      <c r="O986">
+        <v>1</v>
+      </c>
+      <c r="P986" t="s">
+        <v>541</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-00753-601111.xlsx
+++ b/s60_signal/position-00753-601111.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="543">
   <si>
     <t>trade_time</t>
   </si>
@@ -1625,6 +1625,9 @@
   </si>
   <si>
     <t>2020-11-05</t>
+  </si>
+  <si>
+    <t>2021-09-15</t>
   </si>
   <si>
     <t>2021-09-16</t>
@@ -1997,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P986"/>
+  <dimension ref="A1:P987"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -51055,28 +51058,28 @@
         <v>100</v>
       </c>
       <c r="C982">
-        <v>0.7589034565682784</v>
+        <v>0.8361670111513115</v>
       </c>
       <c r="D982" t="s">
         <v>239</v>
       </c>
       <c r="E982">
-        <v>1.546943243945176</v>
+        <v>1.629952424896419</v>
       </c>
       <c r="F982">
         <v>1</v>
       </c>
       <c r="G982">
-        <v>0.01372109654343172</v>
+        <v>0.01364383298884869</v>
       </c>
       <c r="H982">
-        <v>0.01547305675605482</v>
+        <v>0.01539004757510358</v>
       </c>
       <c r="I982">
-        <v>0.7880397873768974</v>
+        <v>0.7937854137451072</v>
       </c>
       <c r="J982">
-        <v>1.268316349008165</v>
+        <v>1.253196279618139</v>
       </c>
       <c r="K982">
         <v>5.11</v>
@@ -51105,28 +51108,28 @@
         <v>100</v>
       </c>
       <c r="C983">
-        <v>0.7508620194677098</v>
+        <v>0.7589034565682784</v>
       </c>
       <c r="D983" t="s">
         <v>239</v>
       </c>
       <c r="E983">
-        <v>1.538303813479007</v>
+        <v>1.546943243945176</v>
       </c>
       <c r="F983">
         <v>1</v>
       </c>
       <c r="G983">
-        <v>0.01372913798053229</v>
+        <v>0.01372109654343172</v>
       </c>
       <c r="H983">
-        <v>0.01548169618652099</v>
+        <v>0.01547305675605482</v>
       </c>
       <c r="I983">
-        <v>0.787441794011297</v>
+        <v>0.7880397873768974</v>
       </c>
       <c r="J983">
-        <v>1.269890015759744</v>
+        <v>1.268316349008165</v>
       </c>
       <c r="K983">
         <v>5.11</v>
@@ -51155,28 +51158,28 @@
         <v>100</v>
       </c>
       <c r="C984">
-        <v>0.7598146472136049</v>
+        <v>0.7508620194677098</v>
       </c>
       <c r="D984" t="s">
         <v>239</v>
       </c>
       <c r="E984">
-        <v>1.547922194364518</v>
+        <v>1.538303813479007</v>
       </c>
       <c r="F984">
         <v>1</v>
       </c>
       <c r="G984">
-        <v>0.01372018535278639</v>
+        <v>0.01372913798053229</v>
       </c>
       <c r="H984">
-        <v>0.01547207780563548</v>
+        <v>0.01548169618652099</v>
       </c>
       <c r="I984">
-        <v>0.7881075471509131</v>
+        <v>0.787441794011297</v>
       </c>
       <c r="J984">
-        <v>1.268138033813385</v>
+        <v>1.269890015759744</v>
       </c>
       <c r="K984">
         <v>5.11</v>
@@ -51205,28 +51208,28 @@
         <v>100</v>
       </c>
       <c r="C985">
-        <v>0.7489382777012477</v>
+        <v>0.7598146472136049</v>
       </c>
       <c r="D985" t="s">
         <v>239</v>
       </c>
       <c r="E985">
-        <v>1.536237014594882</v>
+        <v>1.547922194364518</v>
       </c>
       <c r="F985">
         <v>1</v>
       </c>
       <c r="G985">
-        <v>0.01373106172229875</v>
+        <v>0.01372018535278639</v>
       </c>
       <c r="H985">
-        <v>0.01548376298540512</v>
+        <v>0.01547207780563548</v>
       </c>
       <c r="I985">
-        <v>0.7872987368936348</v>
+        <v>0.7881075471509131</v>
       </c>
       <c r="J985">
-        <v>1.270266481858856</v>
+        <v>1.268138033813385</v>
       </c>
       <c r="K985">
         <v>5.11</v>
@@ -51255,28 +51258,28 @@
         <v>100</v>
       </c>
       <c r="C986">
-        <v>0.7626869004855017</v>
+        <v>0.7489382777012477</v>
       </c>
       <c r="D986" t="s">
         <v>239</v>
       </c>
       <c r="E986">
-        <v>1.551008039856243</v>
+        <v>1.536237014594882</v>
       </c>
       <c r="F986">
         <v>1</v>
       </c>
       <c r="G986">
-        <v>0.0137173130995145</v>
+        <v>0.01373106172229875</v>
       </c>
       <c r="H986">
-        <v>0.01546899196014376</v>
+        <v>0.01548376298540512</v>
       </c>
       <c r="I986">
-        <v>0.7883211393707414</v>
+        <v>0.7872987368936348</v>
       </c>
       <c r="J986">
-        <v>1.267575949024364</v>
+        <v>1.270266481858856</v>
       </c>
       <c r="K986">
         <v>5.11</v>
@@ -51295,6 +51298,56 @@
       </c>
       <c r="P986" t="s">
         <v>541</v>
+      </c>
+    </row>
+    <row r="987" spans="1:16">
+      <c r="A987" s="1">
+        <v>0</v>
+      </c>
+      <c r="B987" t="s">
+        <v>100</v>
+      </c>
+      <c r="C987">
+        <v>0.7626869004855017</v>
+      </c>
+      <c r="D987" t="s">
+        <v>239</v>
+      </c>
+      <c r="E987">
+        <v>1.551008039856243</v>
+      </c>
+      <c r="F987">
+        <v>1</v>
+      </c>
+      <c r="G987">
+        <v>0.0137173130995145</v>
+      </c>
+      <c r="H987">
+        <v>0.01546899196014376</v>
+      </c>
+      <c r="I987">
+        <v>0.7883211393707414</v>
+      </c>
+      <c r="J987">
+        <v>1.267575949024364</v>
+      </c>
+      <c r="K987">
+        <v>5.11</v>
+      </c>
+      <c r="L987">
+        <v>7.24</v>
+      </c>
+      <c r="M987">
+        <v>5.49</v>
+      </c>
+      <c r="N987">
+        <v>8.51</v>
+      </c>
+      <c r="O987">
+        <v>1</v>
+      </c>
+      <c r="P987" t="s">
+        <v>542</v>
       </c>
     </row>
   </sheetData>
